--- a/data/raw/monthly_summary.xlsx
+++ b/data/raw/monthly_summary.xlsx
@@ -499,10 +499,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>205286.01</v>
+        <v>208116.18</v>
       </c>
       <c r="I2" t="n">
-        <v>174174.17</v>
+        <v>176552.24</v>
       </c>
       <c r="J2" t="n">
         <v>22</v>
@@ -539,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>242603.82</v>
+        <v>213219.29</v>
       </c>
       <c r="I3" t="n">
-        <v>206375.78</v>
+        <v>179202.98</v>
       </c>
       <c r="J3" t="n">
         <v>13</v>
@@ -579,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>209511.12</v>
+        <v>228604.96</v>
       </c>
       <c r="I4" t="n">
-        <v>177088.99</v>
+        <v>192654.28</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -619,10 +619,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>108519.09</v>
+        <v>102427.86</v>
       </c>
       <c r="I5" t="n">
-        <v>104251.22</v>
+        <v>91454.50999999999</v>
       </c>
       <c r="J5" t="n">
         <v>11</v>
@@ -659,10 +659,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>125999.24</v>
+        <v>87368.66</v>
       </c>
       <c r="I6" t="n">
-        <v>104907.26</v>
+        <v>87602.13</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>131963.92</v>
+        <v>98831.21000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>102766.82</v>
+        <v>97973.99000000001</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>209502.47</v>
+        <v>221765.9</v>
       </c>
       <c r="H8" t="n">
-        <v>75915.63</v>
+        <v>72852.45</v>
       </c>
       <c r="I8" t="n">
-        <v>75212.5</v>
+        <v>73609.33</v>
       </c>
       <c r="J8" t="n">
         <v>19</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>133842.21</v>
+        <v>139557.99</v>
       </c>
       <c r="H9" t="n">
-        <v>74711.56</v>
+        <v>71999.72</v>
       </c>
       <c r="I9" t="n">
-        <v>73898.83</v>
+        <v>70191.72</v>
       </c>
       <c r="J9" t="n">
         <v>11</v>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>91628.87</v>
+        <v>97790.34</v>
       </c>
       <c r="H10" t="n">
-        <v>82420.3</v>
+        <v>77156.92</v>
       </c>
       <c r="I10" t="n">
-        <v>82209.03999999999</v>
+        <v>77020.45</v>
       </c>
       <c r="J10" t="n">
         <v>7</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>50599.95</v>
+        <v>53825.59</v>
       </c>
       <c r="I11" t="n">
-        <v>52334.23</v>
+        <v>53892.97</v>
       </c>
       <c r="J11" t="n">
         <v>7</v>
@@ -899,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>57510.86</v>
+        <v>53715.09</v>
       </c>
       <c r="I12" t="n">
-        <v>55711.46</v>
+        <v>53996.82</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -939,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>57031.34</v>
+        <v>44492</v>
       </c>
       <c r="I13" t="n">
-        <v>58502.48</v>
+        <v>45227.29</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
@@ -979,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>94857.92999999999</v>
+        <v>87525.33</v>
       </c>
       <c r="I14" t="n">
-        <v>96772.69</v>
+        <v>86687.42999999999</v>
       </c>
       <c r="J14" t="n">
         <v>15</v>
@@ -1019,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>82485.06</v>
+        <v>77033.60000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>83459.78999999999</v>
+        <v>78732.23</v>
       </c>
       <c r="J15" t="n">
         <v>9</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>79749.39999999999</v>
+        <v>86822.42</v>
       </c>
       <c r="I16" t="n">
-        <v>79106.12</v>
+        <v>85150.23</v>
       </c>
       <c r="J16" t="n">
         <v>6</v>
@@ -1099,10 +1099,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>213108.12</v>
+        <v>215612.78</v>
       </c>
       <c r="I17" t="n">
-        <v>181956.56</v>
+        <v>182773.44</v>
       </c>
       <c r="J17" t="n">
         <v>22</v>
@@ -1139,10 +1139,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>197487.34</v>
+        <v>226629.86</v>
       </c>
       <c r="I18" t="n">
-        <v>166797.72</v>
+        <v>192352.56</v>
       </c>
       <c r="J18" t="n">
         <v>13</v>
@@ -1179,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>215009.41</v>
+        <v>201098.23</v>
       </c>
       <c r="I19" t="n">
-        <v>182418.34</v>
+        <v>169622.93</v>
       </c>
       <c r="J19" t="n">
         <v>9</v>
@@ -1219,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>98988.06</v>
+        <v>99816.61</v>
       </c>
       <c r="I20" t="n">
-        <v>101920.89</v>
+        <v>86227.75999999999</v>
       </c>
       <c r="J20" t="n">
         <v>11</v>
@@ -1259,10 +1259,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>81990.59</v>
+        <v>110487.13</v>
       </c>
       <c r="I21" t="n">
-        <v>83484.44</v>
+        <v>111210.05</v>
       </c>
       <c r="J21" t="n">
         <v>6</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>93644.42999999999</v>
+        <v>101171.79</v>
       </c>
       <c r="I22" t="n">
-        <v>90813.62</v>
+        <v>102119.75</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>233702.42</v>
+        <v>236435.83</v>
       </c>
       <c r="H23" t="n">
-        <v>75549.10000000001</v>
+        <v>77438</v>
       </c>
       <c r="I23" t="n">
-        <v>73223.57000000001</v>
+        <v>75905.27</v>
       </c>
       <c r="J23" t="n">
         <v>19</v>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>135447.48</v>
+        <v>141587.88</v>
       </c>
       <c r="H24" t="n">
-        <v>71795.10000000001</v>
+        <v>75635.98</v>
       </c>
       <c r="I24" t="n">
-        <v>70980.48</v>
+        <v>76395.36</v>
       </c>
       <c r="J24" t="n">
         <v>11</v>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>91827.32000000001</v>
+        <v>92686.3</v>
       </c>
       <c r="H25" t="n">
-        <v>70858.38</v>
+        <v>61858.27</v>
       </c>
       <c r="I25" t="n">
-        <v>69641.98</v>
+        <v>62943.12</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>50323.65</v>
+        <v>50079.81</v>
       </c>
       <c r="I26" t="n">
-        <v>51630.27</v>
+        <v>49761.06</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
@@ -1499,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>47317</v>
+        <v>51627.14</v>
       </c>
       <c r="I27" t="n">
-        <v>47119.38</v>
+        <v>51322.59</v>
       </c>
       <c r="J27" t="n">
         <v>4</v>
@@ -1539,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>53543.4</v>
+        <v>54484.84</v>
       </c>
       <c r="I28" t="n">
-        <v>53370.08</v>
+        <v>55688.08</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -1579,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>84679.86</v>
+        <v>80921.53</v>
       </c>
       <c r="I29" t="n">
-        <v>85987.39</v>
+        <v>81359.52</v>
       </c>
       <c r="J29" t="n">
         <v>15</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>82019.09</v>
+        <v>86344.53999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>82432.78</v>
+        <v>85181.81</v>
       </c>
       <c r="J30" t="n">
         <v>9</v>
@@ -1659,10 +1659,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>80998.64</v>
+        <v>89623.56</v>
       </c>
       <c r="I31" t="n">
-        <v>82220</v>
+        <v>88442.11</v>
       </c>
       <c r="J31" t="n">
         <v>6</v>
@@ -1699,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>214885.17</v>
+        <v>199701.44</v>
       </c>
       <c r="I32" t="n">
-        <v>182292.09</v>
+        <v>168351.26</v>
       </c>
       <c r="J32" t="n">
         <v>22</v>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>238010.11</v>
+        <v>228976.39</v>
       </c>
       <c r="I33" t="n">
-        <v>201052.37</v>
+        <v>193637.55</v>
       </c>
       <c r="J33" t="n">
         <v>13</v>
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>200380.55</v>
+        <v>216497.63</v>
       </c>
       <c r="I34" t="n">
-        <v>168838.05</v>
+        <v>182960.27</v>
       </c>
       <c r="J34" t="n">
         <v>9</v>
@@ -1819,10 +1819,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>93326.81</v>
+        <v>122856.32</v>
       </c>
       <c r="I35" t="n">
-        <v>92318.74000000001</v>
+        <v>97694.45</v>
       </c>
       <c r="J35" t="n">
         <v>11</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>110454.99</v>
+        <v>95617.96000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>109546.02</v>
+        <v>93630.25999999999</v>
       </c>
       <c r="J36" t="n">
         <v>6</v>
@@ -1899,10 +1899,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>122119.73</v>
+        <v>96728.41</v>
       </c>
       <c r="I37" t="n">
-        <v>103533.56</v>
+        <v>96181.08</v>
       </c>
       <c r="J37" t="n">
         <v>4</v>
@@ -1936,13 +1936,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>255327.53</v>
+        <v>253486.6</v>
       </c>
       <c r="H38" t="n">
-        <v>69013.71000000001</v>
+        <v>75825.61</v>
       </c>
       <c r="I38" t="n">
-        <v>70192.39999999999</v>
+        <v>74892.19</v>
       </c>
       <c r="J38" t="n">
         <v>19</v>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>153964.87</v>
+        <v>156689.7</v>
       </c>
       <c r="H39" t="n">
-        <v>72527.39</v>
+        <v>70150.14</v>
       </c>
       <c r="I39" t="n">
-        <v>72371.11</v>
+        <v>69941.22</v>
       </c>
       <c r="J39" t="n">
         <v>11</v>
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>104495.11</v>
+        <v>111736.72</v>
       </c>
       <c r="H40" t="n">
-        <v>75703.21000000001</v>
+        <v>83395.97</v>
       </c>
       <c r="I40" t="n">
-        <v>73487.74000000001</v>
+        <v>84025.00999999999</v>
       </c>
       <c r="J40" t="n">
         <v>7</v>
@@ -2059,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>54717.29</v>
+        <v>49640.69</v>
       </c>
       <c r="I41" t="n">
-        <v>54236.87</v>
+        <v>50939.6</v>
       </c>
       <c r="J41" t="n">
         <v>7</v>
@@ -2099,10 +2099,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>54031.35</v>
+        <v>55159.12</v>
       </c>
       <c r="I42" t="n">
-        <v>53362.51</v>
+        <v>55089.53</v>
       </c>
       <c r="J42" t="n">
         <v>4</v>
@@ -2139,10 +2139,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>52151.05</v>
+        <v>58111.02</v>
       </c>
       <c r="I43" t="n">
-        <v>51816</v>
+        <v>58065.03</v>
       </c>
       <c r="J43" t="n">
         <v>3</v>
@@ -2179,10 +2179,10 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>79470.44</v>
+        <v>88834.73</v>
       </c>
       <c r="I44" t="n">
-        <v>80786.82000000001</v>
+        <v>88915.73</v>
       </c>
       <c r="J44" t="n">
         <v>15</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>90525.78999999999</v>
+        <v>75938.33</v>
       </c>
       <c r="I45" t="n">
-        <v>88334.58</v>
+        <v>76790.98</v>
       </c>
       <c r="J45" t="n">
         <v>9</v>
@@ -2259,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>86970.94</v>
+        <v>88274.88</v>
       </c>
       <c r="I46" t="n">
-        <v>89178.16</v>
+        <v>86971.03999999999</v>
       </c>
       <c r="J46" t="n">
         <v>6</v>
@@ -2299,10 +2299,10 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>223003.47</v>
+        <v>204635.84</v>
       </c>
       <c r="I47" t="n">
-        <v>188791.93</v>
+        <v>174012.3</v>
       </c>
       <c r="J47" t="n">
         <v>22</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>230341.96</v>
+        <v>237776.63</v>
       </c>
       <c r="I48" t="n">
-        <v>194855.9</v>
+        <v>200260.21</v>
       </c>
       <c r="J48" t="n">
         <v>13</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>216195.14</v>
+        <v>218474.74</v>
       </c>
       <c r="I49" t="n">
-        <v>183652.66</v>
+        <v>183949.23</v>
       </c>
       <c r="J49" t="n">
         <v>9</v>
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>106757.07</v>
+        <v>97834.57000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>88292.57000000001</v>
+        <v>100369.58</v>
       </c>
       <c r="J50" t="n">
         <v>11</v>
@@ -2459,10 +2459,10 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>95527.53999999999</v>
+        <v>99216.16</v>
       </c>
       <c r="I51" t="n">
-        <v>95140.08</v>
+        <v>84580.64</v>
       </c>
       <c r="J51" t="n">
         <v>6</v>
@@ -2499,10 +2499,10 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>96591.00999999999</v>
+        <v>95795.89999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>98618.64999999999</v>
+        <v>93988.38</v>
       </c>
       <c r="J52" t="n">
         <v>4</v>
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>234906.04</v>
+        <v>263270.98</v>
       </c>
       <c r="H53" t="n">
-        <v>87178.60000000001</v>
+        <v>72828.59</v>
       </c>
       <c r="I53" t="n">
-        <v>86652.27</v>
+        <v>72345.77</v>
       </c>
       <c r="J53" t="n">
         <v>19</v>
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>157566.52</v>
+        <v>157542.45</v>
       </c>
       <c r="H54" t="n">
-        <v>74576.92999999999</v>
+        <v>79177.17999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>74073.25999999999</v>
+        <v>80400.14999999999</v>
       </c>
       <c r="J54" t="n">
         <v>11</v>
@@ -2616,13 +2616,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>114307.96</v>
+        <v>103621.2</v>
       </c>
       <c r="H55" t="n">
-        <v>83820.58</v>
+        <v>80491.63</v>
       </c>
       <c r="I55" t="n">
-        <v>85180.81</v>
+        <v>79591.58</v>
       </c>
       <c r="J55" t="n">
         <v>7</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>57970.28</v>
+        <v>51655.42</v>
       </c>
       <c r="I56" t="n">
-        <v>57276.61</v>
+        <v>52118.97</v>
       </c>
       <c r="J56" t="n">
         <v>7</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>53096.26</v>
+        <v>55853.92</v>
       </c>
       <c r="I57" t="n">
-        <v>52600.8</v>
+        <v>54449.46</v>
       </c>
       <c r="J57" t="n">
         <v>4</v>
@@ -2739,10 +2739,10 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>51870.93</v>
+        <v>58242.31</v>
       </c>
       <c r="I58" t="n">
-        <v>50897.85</v>
+        <v>58083.7</v>
       </c>
       <c r="J58" t="n">
         <v>3</v>
@@ -2779,10 +2779,10 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>84202.89</v>
+        <v>80555.78999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>84519.99000000001</v>
+        <v>77844.53</v>
       </c>
       <c r="J59" t="n">
         <v>15</v>
@@ -2819,10 +2819,10 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>85759.12</v>
+        <v>83631.57000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>84100.39999999999</v>
+        <v>82911.35000000001</v>
       </c>
       <c r="J60" t="n">
         <v>9</v>
@@ -2859,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>74853.21000000001</v>
+        <v>90000.57000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>75010.87</v>
+        <v>89621.44</v>
       </c>
       <c r="J61" t="n">
         <v>6</v>
@@ -2899,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>190056.39</v>
+        <v>229238.97</v>
       </c>
       <c r="I62" t="n">
-        <v>159570.52</v>
+        <v>193797.27</v>
       </c>
       <c r="J62" t="n">
         <v>22</v>
@@ -2939,10 +2939,10 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>222852.73</v>
+        <v>214542.19</v>
       </c>
       <c r="I63" t="n">
-        <v>187617.7</v>
+        <v>180522.4</v>
       </c>
       <c r="J63" t="n">
         <v>13</v>
@@ -2979,10 +2979,10 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>186065.35</v>
+        <v>198900.81</v>
       </c>
       <c r="I64" t="n">
-        <v>156045.61</v>
+        <v>168413.02</v>
       </c>
       <c r="J64" t="n">
         <v>9</v>
@@ -3019,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>96209.71000000001</v>
+        <v>98509.97</v>
       </c>
       <c r="I65" t="n">
-        <v>94166.5</v>
+        <v>99688.32000000001</v>
       </c>
       <c r="J65" t="n">
         <v>11</v>
@@ -3059,10 +3059,10 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>133695.89</v>
+        <v>123055.57</v>
       </c>
       <c r="I66" t="n">
-        <v>96057.75999999999</v>
+        <v>95644.33</v>
       </c>
       <c r="J66" t="n">
         <v>6</v>
@@ -3099,10 +3099,10 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>96860.88</v>
+        <v>82369.42999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>94906.57000000001</v>
+        <v>82296.05</v>
       </c>
       <c r="J67" t="n">
         <v>4</v>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>281036.45</v>
+        <v>283621.7</v>
       </c>
       <c r="H68" t="n">
-        <v>74167.8</v>
+        <v>75566.08</v>
       </c>
       <c r="I68" t="n">
-        <v>72621.57000000001</v>
+        <v>74933.24000000001</v>
       </c>
       <c r="J68" t="n">
         <v>19</v>
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>155702.73</v>
+        <v>153621.34</v>
       </c>
       <c r="H69" t="n">
-        <v>77918.02</v>
+        <v>84388.27</v>
       </c>
       <c r="I69" t="n">
-        <v>76663.28999999999</v>
+        <v>84336.28</v>
       </c>
       <c r="J69" t="n">
         <v>11</v>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>101438.93</v>
+        <v>99738.83</v>
       </c>
       <c r="H70" t="n">
-        <v>73500.58</v>
+        <v>84621.42</v>
       </c>
       <c r="I70" t="n">
-        <v>72433.62</v>
+        <v>86221.78</v>
       </c>
       <c r="J70" t="n">
         <v>7</v>
@@ -3259,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>50637.85</v>
+        <v>56352.42</v>
       </c>
       <c r="I71" t="n">
-        <v>51423.47</v>
+        <v>57000.02</v>
       </c>
       <c r="J71" t="n">
         <v>7</v>
@@ -3299,10 +3299,10 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>57066.66</v>
+        <v>56952.7</v>
       </c>
       <c r="I72" t="n">
-        <v>56661.29</v>
+        <v>57208.26</v>
       </c>
       <c r="J72" t="n">
         <v>4</v>
@@ -3339,10 +3339,10 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>49901.14</v>
+        <v>54789.02</v>
       </c>
       <c r="I73" t="n">
-        <v>50154.75</v>
+        <v>53342.26</v>
       </c>
       <c r="J73" t="n">
         <v>3</v>
@@ -3379,10 +3379,10 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>84041.99000000001</v>
+        <v>93772.89999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>86593.88</v>
+        <v>94758.92</v>
       </c>
       <c r="J74" t="n">
         <v>15</v>
@@ -3419,10 +3419,10 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>88215.83</v>
+        <v>85651.52</v>
       </c>
       <c r="I75" t="n">
-        <v>87087.19</v>
+        <v>85584.36</v>
       </c>
       <c r="J75" t="n">
         <v>9</v>
@@ -3459,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>78181.50999999999</v>
+        <v>89377.96000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>77734.61</v>
+        <v>86730.36</v>
       </c>
       <c r="J76" t="n">
         <v>6</v>
@@ -3499,10 +3499,10 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>218001.91</v>
+        <v>222941.56</v>
       </c>
       <c r="I77" t="n">
-        <v>184694.23</v>
+        <v>189049.46</v>
       </c>
       <c r="J77" t="n">
         <v>22</v>
@@ -3539,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>212175.77</v>
+        <v>220117.34</v>
       </c>
       <c r="I78" t="n">
-        <v>178322.38</v>
+        <v>184380.09</v>
       </c>
       <c r="J78" t="n">
         <v>13</v>
@@ -3579,10 +3579,10 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>199357.03</v>
+        <v>208586.2</v>
       </c>
       <c r="I79" t="n">
-        <v>168679.17</v>
+        <v>176867.72</v>
       </c>
       <c r="J79" t="n">
         <v>9</v>
@@ -3619,10 +3619,10 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>100007.75</v>
+        <v>128427.24</v>
       </c>
       <c r="I80" t="n">
-        <v>98000.57000000001</v>
+        <v>98824.87</v>
       </c>
       <c r="J80" t="n">
         <v>11</v>
@@ -3659,10 +3659,10 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>117566.8</v>
+        <v>97601.48</v>
       </c>
       <c r="I81" t="n">
-        <v>100040.89</v>
+        <v>97964.28</v>
       </c>
       <c r="J81" t="n">
         <v>6</v>
@@ -3699,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>86819.7</v>
+        <v>84329.03999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>88591.45</v>
+        <v>84547.64</v>
       </c>
       <c r="J82" t="n">
         <v>4</v>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>261952.76</v>
+        <v>240692.68</v>
       </c>
       <c r="H83" t="n">
-        <v>86295.99000000001</v>
+        <v>79214.47</v>
       </c>
       <c r="I83" t="n">
-        <v>85491.07000000001</v>
+        <v>79286.82000000001</v>
       </c>
       <c r="J83" t="n">
         <v>19</v>
@@ -3776,13 +3776,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>165142.41</v>
+        <v>156714.62</v>
       </c>
       <c r="H84" t="n">
-        <v>75050.72</v>
+        <v>76170.31</v>
       </c>
       <c r="I84" t="n">
-        <v>75549.36</v>
+        <v>76582.24000000001</v>
       </c>
       <c r="J84" t="n">
         <v>11</v>
@@ -3816,13 +3816,13 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>99609.91</v>
+        <v>95743.47</v>
       </c>
       <c r="H85" t="n">
-        <v>71935.89999999999</v>
+        <v>83608.67</v>
       </c>
       <c r="I85" t="n">
-        <v>72677.39</v>
+        <v>85310.49000000001</v>
       </c>
       <c r="J85" t="n">
         <v>7</v>
@@ -3859,10 +3859,10 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>55406.15</v>
+        <v>52471.47</v>
       </c>
       <c r="I86" t="n">
-        <v>55196.76</v>
+        <v>51856.84</v>
       </c>
       <c r="J86" t="n">
         <v>7</v>
@@ -3899,10 +3899,10 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>58165.19</v>
+        <v>55090.16</v>
       </c>
       <c r="I87" t="n">
-        <v>58096.58</v>
+        <v>54398.52</v>
       </c>
       <c r="J87" t="n">
         <v>4</v>
@@ -3939,10 +3939,10 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>52099.02</v>
+        <v>46504.2</v>
       </c>
       <c r="I88" t="n">
-        <v>51298.05</v>
+        <v>46700.3</v>
       </c>
       <c r="J88" t="n">
         <v>3</v>
@@ -3979,10 +3979,10 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>80165.61</v>
+        <v>77056.33</v>
       </c>
       <c r="I89" t="n">
-        <v>81241.34</v>
+        <v>77570.11</v>
       </c>
       <c r="J89" t="n">
         <v>15</v>
@@ -4019,10 +4019,10 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>78140.7</v>
+        <v>96983.28999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>77933.44</v>
+        <v>95306.81</v>
       </c>
       <c r="J90" t="n">
         <v>9</v>
@@ -4059,10 +4059,10 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>85899.53999999999</v>
+        <v>81201.2</v>
       </c>
       <c r="I91" t="n">
-        <v>84655.63</v>
+        <v>80355.48</v>
       </c>
       <c r="J91" t="n">
         <v>6</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>243130.33</v>
+        <v>207760.32</v>
       </c>
       <c r="I92" t="n">
-        <v>208149.18</v>
+        <v>174812.12</v>
       </c>
       <c r="J92" t="n">
         <v>22</v>
@@ -4139,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>218462.31</v>
+        <v>217528.1</v>
       </c>
       <c r="I93" t="n">
-        <v>184822.04</v>
+        <v>183240.63</v>
       </c>
       <c r="J93" t="n">
         <v>13</v>
@@ -4179,10 +4179,10 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>221868.54</v>
+        <v>203504.59</v>
       </c>
       <c r="I94" t="n">
-        <v>186060.21</v>
+        <v>171832.02</v>
       </c>
       <c r="J94" t="n">
         <v>9</v>
@@ -4219,10 +4219,10 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>101281.29</v>
+        <v>95179.5</v>
       </c>
       <c r="I95" t="n">
-        <v>86004.48</v>
+        <v>92752.31</v>
       </c>
       <c r="J95" t="n">
         <v>11</v>
@@ -4259,10 +4259,10 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>86537.81</v>
+        <v>141420.88</v>
       </c>
       <c r="I96" t="n">
-        <v>86504.09</v>
+        <v>91465.24000000001</v>
       </c>
       <c r="J96" t="n">
         <v>6</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>113744.99</v>
+        <v>91978.23</v>
       </c>
       <c r="I97" t="n">
-        <v>88681.41</v>
+        <v>90513.78</v>
       </c>
       <c r="J97" t="n">
         <v>4</v>
@@ -4336,13 +4336,13 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>246573.59</v>
+        <v>256748.38</v>
       </c>
       <c r="H98" t="n">
-        <v>83202.32000000001</v>
+        <v>67264.87</v>
       </c>
       <c r="I98" t="n">
-        <v>83134.12</v>
+        <v>66045.63</v>
       </c>
       <c r="J98" t="n">
         <v>19</v>
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>136849.34</v>
+        <v>147319.16</v>
       </c>
       <c r="H99" t="n">
-        <v>76337.88</v>
+        <v>74216.89999999999</v>
       </c>
       <c r="I99" t="n">
-        <v>75011.63</v>
+        <v>73689.12</v>
       </c>
       <c r="J99" t="n">
         <v>11</v>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>108633.94</v>
+        <v>98063.55</v>
       </c>
       <c r="H100" t="n">
-        <v>62865.27</v>
+        <v>82090.67999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>64134.36</v>
+        <v>82660.13</v>
       </c>
       <c r="J100" t="n">
         <v>7</v>
@@ -4459,10 +4459,10 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>53407</v>
+        <v>52879.17</v>
       </c>
       <c r="I101" t="n">
-        <v>53158.09</v>
+        <v>55287.34</v>
       </c>
       <c r="J101" t="n">
         <v>7</v>
@@ -4499,10 +4499,10 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>55014.22</v>
+        <v>56030.57</v>
       </c>
       <c r="I102" t="n">
-        <v>52941.3</v>
+        <v>55153.55</v>
       </c>
       <c r="J102" t="n">
         <v>4</v>
@@ -4539,10 +4539,10 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>59726.94</v>
+        <v>56899.84</v>
       </c>
       <c r="I103" t="n">
-        <v>58970.51</v>
+        <v>57860.61</v>
       </c>
       <c r="J103" t="n">
         <v>3</v>
@@ -4579,10 +4579,10 @@
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>91023.63</v>
+        <v>75761.12</v>
       </c>
       <c r="I104" t="n">
-        <v>89852.53999999999</v>
+        <v>75508.97</v>
       </c>
       <c r="J104" t="n">
         <v>15</v>
@@ -4619,10 +4619,10 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>94182.52</v>
+        <v>86809.50999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>93416.72</v>
+        <v>86425.44</v>
       </c>
       <c r="J105" t="n">
         <v>9</v>
@@ -4659,10 +4659,10 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>70650.85000000001</v>
+        <v>81611.53999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>70990.61</v>
+        <v>84862.06</v>
       </c>
       <c r="J106" t="n">
         <v>6</v>
@@ -4699,10 +4699,10 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>212811.46</v>
+        <v>212880.99</v>
       </c>
       <c r="I107" t="n">
-        <v>179303.17</v>
+        <v>179795.04</v>
       </c>
       <c r="J107" t="n">
         <v>22</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>220428.47</v>
+        <v>225483.07</v>
       </c>
       <c r="I108" t="n">
-        <v>186457.65</v>
+        <v>189599.04</v>
       </c>
       <c r="J108" t="n">
         <v>13</v>
@@ -4779,10 +4779,10 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>205403.61</v>
+        <v>209166.11</v>
       </c>
       <c r="I109" t="n">
-        <v>174172.17</v>
+        <v>174881.34</v>
       </c>
       <c r="J109" t="n">
         <v>9</v>
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>87231.11</v>
+        <v>82015.85000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>87689.2</v>
+        <v>82390.62</v>
       </c>
       <c r="J110" t="n">
         <v>11</v>
@@ -4859,10 +4859,10 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>113596.68</v>
+        <v>105643.68</v>
       </c>
       <c r="I111" t="n">
-        <v>99212.27</v>
+        <v>104020.09</v>
       </c>
       <c r="J111" t="n">
         <v>6</v>
@@ -4899,10 +4899,10 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>98173.42999999999</v>
+        <v>90154.66</v>
       </c>
       <c r="I112" t="n">
-        <v>98921.16</v>
+        <v>89232.07000000001</v>
       </c>
       <c r="J112" t="n">
         <v>4</v>
@@ -4936,13 +4936,13 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>261948.39</v>
+        <v>267979.01</v>
       </c>
       <c r="H113" t="n">
-        <v>76395.42</v>
+        <v>70647.24000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>77106.42999999999</v>
+        <v>72904.60000000001</v>
       </c>
       <c r="J113" t="n">
         <v>19</v>
@@ -4976,13 +4976,13 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>155630.43</v>
+        <v>142351.99</v>
       </c>
       <c r="H114" t="n">
-        <v>80288.14</v>
+        <v>77556.39</v>
       </c>
       <c r="I114" t="n">
-        <v>79175.16</v>
+        <v>76300.53</v>
       </c>
       <c r="J114" t="n">
         <v>11</v>
@@ -5016,13 +5016,13 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>101989.76</v>
+        <v>106841.55</v>
       </c>
       <c r="H115" t="n">
-        <v>70281.00999999999</v>
+        <v>88052.50999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>73160.12</v>
+        <v>88101.71000000001</v>
       </c>
       <c r="J115" t="n">
         <v>7</v>
@@ -5059,10 +5059,10 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>56472.66</v>
+        <v>54096.56</v>
       </c>
       <c r="I116" t="n">
-        <v>57030.04</v>
+        <v>54146.93</v>
       </c>
       <c r="J116" t="n">
         <v>7</v>
@@ -5099,10 +5099,10 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>57962.26</v>
+        <v>47569.95</v>
       </c>
       <c r="I117" t="n">
-        <v>56536.84</v>
+        <v>47011.59</v>
       </c>
       <c r="J117" t="n">
         <v>4</v>
@@ -5139,10 +5139,10 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>58336.58</v>
+        <v>56562.55</v>
       </c>
       <c r="I118" t="n">
-        <v>56706.54</v>
+        <v>57383.5</v>
       </c>
       <c r="J118" t="n">
         <v>3</v>
@@ -5179,10 +5179,10 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>78435.13</v>
+        <v>88694.3</v>
       </c>
       <c r="I119" t="n">
-        <v>77084.28999999999</v>
+        <v>85769.11</v>
       </c>
       <c r="J119" t="n">
         <v>15</v>
@@ -5219,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>83617.00999999999</v>
+        <v>86495.02</v>
       </c>
       <c r="I120" t="n">
-        <v>81952.25999999999</v>
+        <v>83353.12</v>
       </c>
       <c r="J120" t="n">
         <v>9</v>
@@ -5259,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>82024.33</v>
+        <v>90012.27</v>
       </c>
       <c r="I121" t="n">
-        <v>82453.95</v>
+        <v>91444.69</v>
       </c>
       <c r="J121" t="n">
         <v>6</v>
@@ -5299,10 +5299,10 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>210333.84</v>
+        <v>199660.77</v>
       </c>
       <c r="I122" t="n">
-        <v>177298.39</v>
+        <v>169330.48</v>
       </c>
       <c r="J122" t="n">
         <v>22</v>
@@ -5339,10 +5339,10 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>209045.29</v>
+        <v>251779.56</v>
       </c>
       <c r="I123" t="n">
-        <v>176758.35</v>
+        <v>213450.46</v>
       </c>
       <c r="J123" t="n">
         <v>13</v>
@@ -5379,10 +5379,10 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>211236.18</v>
+        <v>202426.95</v>
       </c>
       <c r="I124" t="n">
-        <v>178407.41</v>
+        <v>169990.38</v>
       </c>
       <c r="J124" t="n">
         <v>9</v>
@@ -5419,10 +5419,10 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>94545.25999999999</v>
+        <v>95738.37</v>
       </c>
       <c r="I125" t="n">
-        <v>93906.06</v>
+        <v>98344.31</v>
       </c>
       <c r="J125" t="n">
         <v>11</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>103125.39</v>
+        <v>93503.28999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>102503.58</v>
+        <v>93060.44</v>
       </c>
       <c r="J126" t="n">
         <v>6</v>
@@ -5499,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>91158.28</v>
+        <v>117898.8</v>
       </c>
       <c r="I127" t="n">
-        <v>90376.23</v>
+        <v>104464.09</v>
       </c>
       <c r="J127" t="n">
         <v>4</v>
@@ -5536,13 +5536,13 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>255048.04</v>
+        <v>247095.57</v>
       </c>
       <c r="H128" t="n">
-        <v>72370.67</v>
+        <v>67405.14</v>
       </c>
       <c r="I128" t="n">
-        <v>73006.35000000001</v>
+        <v>65984.77</v>
       </c>
       <c r="J128" t="n">
         <v>19</v>
@@ -5576,13 +5576,13 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>145742.14</v>
+        <v>140304.42</v>
       </c>
       <c r="H129" t="n">
-        <v>80766.36</v>
+        <v>67917.45</v>
       </c>
       <c r="I129" t="n">
-        <v>78716.32000000001</v>
+        <v>68246.77</v>
       </c>
       <c r="J129" t="n">
         <v>11</v>
@@ -5616,13 +5616,13 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>111338.73</v>
+        <v>96226.84</v>
       </c>
       <c r="H130" t="n">
-        <v>70811.06</v>
+        <v>83279.88</v>
       </c>
       <c r="I130" t="n">
-        <v>70809.31</v>
+        <v>83132.98</v>
       </c>
       <c r="J130" t="n">
         <v>7</v>
@@ -5659,10 +5659,10 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>53316.12</v>
+        <v>53410.78</v>
       </c>
       <c r="I131" t="n">
-        <v>53909.07</v>
+        <v>53907.57</v>
       </c>
       <c r="J131" t="n">
         <v>7</v>
@@ -5699,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>55732.41</v>
+        <v>50052.95</v>
       </c>
       <c r="I132" t="n">
-        <v>54120.81</v>
+        <v>50096.91</v>
       </c>
       <c r="J132" t="n">
         <v>4</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>48201.71</v>
+        <v>53555.28</v>
       </c>
       <c r="I133" t="n">
-        <v>47709.09</v>
+        <v>53395.27</v>
       </c>
       <c r="J133" t="n">
         <v>3</v>
@@ -5779,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>86480.32000000001</v>
+        <v>81412.85000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>86249.09</v>
+        <v>81228.32000000001</v>
       </c>
       <c r="J134" t="n">
         <v>15</v>
@@ -5819,10 +5819,10 @@
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>72884.35000000001</v>
+        <v>74400.63</v>
       </c>
       <c r="I135" t="n">
-        <v>74104.37</v>
+        <v>73186.22</v>
       </c>
       <c r="J135" t="n">
         <v>9</v>
@@ -5859,10 +5859,10 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>76241.46000000001</v>
+        <v>80822.58</v>
       </c>
       <c r="I136" t="n">
-        <v>75677.42999999999</v>
+        <v>81248.89999999999</v>
       </c>
       <c r="J136" t="n">
         <v>6</v>
@@ -5899,10 +5899,10 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>190352.35</v>
+        <v>210690.31</v>
       </c>
       <c r="I137" t="n">
-        <v>160036.46</v>
+        <v>177617.06</v>
       </c>
       <c r="J137" t="n">
         <v>22</v>
@@ -5939,10 +5939,10 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>209411.8</v>
+        <v>191969.44</v>
       </c>
       <c r="I138" t="n">
-        <v>176394.08</v>
+        <v>161773.41</v>
       </c>
       <c r="J138" t="n">
         <v>13</v>
@@ -5979,10 +5979,10 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>202151.51</v>
+        <v>221280.46</v>
       </c>
       <c r="I139" t="n">
-        <v>170430.81</v>
+        <v>186414.94</v>
       </c>
       <c r="J139" t="n">
         <v>9</v>
@@ -6019,10 +6019,10 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>85271.83</v>
+        <v>114083.75</v>
       </c>
       <c r="I140" t="n">
-        <v>83659.03999999999</v>
+        <v>90718.53</v>
       </c>
       <c r="J140" t="n">
         <v>11</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>106019.14</v>
+        <v>89084.59</v>
       </c>
       <c r="I141" t="n">
-        <v>103940.51</v>
+        <v>90557.08</v>
       </c>
       <c r="J141" t="n">
         <v>6</v>
@@ -6099,10 +6099,10 @@
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>127885.03</v>
+        <v>110146.25</v>
       </c>
       <c r="I142" t="n">
-        <v>88931.31</v>
+        <v>99416.63</v>
       </c>
       <c r="J142" t="n">
         <v>4</v>
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>393603.73</v>
+        <v>370688.96</v>
       </c>
       <c r="H143" t="n">
-        <v>75113.91</v>
+        <v>76951.60000000001</v>
       </c>
       <c r="I143" t="n">
-        <v>73960.67999999999</v>
+        <v>78672.02</v>
       </c>
       <c r="J143" t="n">
         <v>19</v>
@@ -6176,13 +6176,13 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>221688.03</v>
+        <v>215836.66</v>
       </c>
       <c r="H144" t="n">
-        <v>72998.96000000001</v>
+        <v>78373.37</v>
       </c>
       <c r="I144" t="n">
-        <v>73242.89999999999</v>
+        <v>79139.63</v>
       </c>
       <c r="J144" t="n">
         <v>11</v>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>153744.77</v>
+        <v>157929.92</v>
       </c>
       <c r="H145" t="n">
-        <v>75106.98</v>
+        <v>84143.69</v>
       </c>
       <c r="I145" t="n">
-        <v>76555.28999999999</v>
+        <v>84408.97</v>
       </c>
       <c r="J145" t="n">
         <v>7</v>
@@ -6259,10 +6259,10 @@
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>55936.09</v>
+        <v>52544.82</v>
       </c>
       <c r="I146" t="n">
-        <v>54997.45</v>
+        <v>53350.67</v>
       </c>
       <c r="J146" t="n">
         <v>7</v>
@@ -6299,10 +6299,10 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>47981.31</v>
+        <v>54036.63</v>
       </c>
       <c r="I147" t="n">
-        <v>47550.79</v>
+        <v>55156.3</v>
       </c>
       <c r="J147" t="n">
         <v>4</v>
@@ -6339,10 +6339,10 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>51953.68</v>
+        <v>52349.5</v>
       </c>
       <c r="I148" t="n">
-        <v>52463.29</v>
+        <v>52307.77</v>
       </c>
       <c r="J148" t="n">
         <v>3</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>94500.37</v>
+        <v>81963.00999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>94983.89999999999</v>
+        <v>79807.67999999999</v>
       </c>
       <c r="J149" t="n">
         <v>15</v>
@@ -6419,10 +6419,10 @@
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>85231.61</v>
+        <v>80220.07000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>85278</v>
+        <v>82490.07000000001</v>
       </c>
       <c r="J150" t="n">
         <v>9</v>
@@ -6459,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>88118.69</v>
+        <v>85276.34</v>
       </c>
       <c r="I151" t="n">
-        <v>87197.92999999999</v>
+        <v>84339.72</v>
       </c>
       <c r="J151" t="n">
         <v>6</v>
@@ -6499,10 +6499,10 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>176765.72</v>
+        <v>204648.93</v>
       </c>
       <c r="I152" t="n">
-        <v>149803.13</v>
+        <v>172897.96</v>
       </c>
       <c r="J152" t="n">
         <v>22</v>
@@ -6539,10 +6539,10 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>227100.88</v>
+        <v>214581.09</v>
       </c>
       <c r="I153" t="n">
-        <v>193028.21</v>
+        <v>181100.33</v>
       </c>
       <c r="J153" t="n">
         <v>13</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>204774.14</v>
+        <v>233052.57</v>
       </c>
       <c r="I154" t="n">
-        <v>174791.06</v>
+        <v>196127.33</v>
       </c>
       <c r="J154" t="n">
         <v>9</v>
@@ -6619,10 +6619,10 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>87361.00999999999</v>
+        <v>85987.92</v>
       </c>
       <c r="I155" t="n">
-        <v>88887.83</v>
+        <v>86090.13</v>
       </c>
       <c r="J155" t="n">
         <v>11</v>
@@ -6659,10 +6659,10 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>88716.14</v>
+        <v>126808.39</v>
       </c>
       <c r="I156" t="n">
-        <v>91286.97</v>
+        <v>99444.14</v>
       </c>
       <c r="J156" t="n">
         <v>6</v>
@@ -6699,10 +6699,10 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>94161.75999999999</v>
+        <v>90605.00999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>93573.3</v>
+        <v>89300.88</v>
       </c>
       <c r="J157" t="n">
         <v>4</v>
@@ -6736,13 +6736,13 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>385401.72</v>
+        <v>373207.39</v>
       </c>
       <c r="H158" t="n">
-        <v>82811.19</v>
+        <v>82944.66</v>
       </c>
       <c r="I158" t="n">
-        <v>83370.25</v>
+        <v>83857.27</v>
       </c>
       <c r="J158" t="n">
         <v>19</v>
@@ -6776,13 +6776,13 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>210618.02</v>
+        <v>230418.01</v>
       </c>
       <c r="H159" t="n">
-        <v>72628.89</v>
+        <v>73148.52</v>
       </c>
       <c r="I159" t="n">
-        <v>71432.09</v>
+        <v>74137.94</v>
       </c>
       <c r="J159" t="n">
         <v>11</v>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>153909.19</v>
+        <v>151701.86</v>
       </c>
       <c r="H160" t="n">
-        <v>72719.10000000001</v>
+        <v>64998.33</v>
       </c>
       <c r="I160" t="n">
-        <v>71405.32000000001</v>
+        <v>66360.02</v>
       </c>
       <c r="J160" t="n">
         <v>7</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>53867.7</v>
+        <v>58422.87</v>
       </c>
       <c r="I161" t="n">
-        <v>53505.65</v>
+        <v>59486.34</v>
       </c>
       <c r="J161" t="n">
         <v>7</v>
@@ -6899,10 +6899,10 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>60430.96</v>
+        <v>49807.8</v>
       </c>
       <c r="I162" t="n">
-        <v>59857.54</v>
+        <v>49958.99</v>
       </c>
       <c r="J162" t="n">
         <v>4</v>
@@ -6939,10 +6939,10 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>53166.76</v>
+        <v>61122.89</v>
       </c>
       <c r="I163" t="n">
-        <v>53178.82</v>
+        <v>62017.87</v>
       </c>
       <c r="J163" t="n">
         <v>3</v>
@@ -6979,10 +6979,10 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>84483.64</v>
+        <v>81561.16</v>
       </c>
       <c r="I164" t="n">
-        <v>87022.36</v>
+        <v>80301.86</v>
       </c>
       <c r="J164" t="n">
         <v>15</v>
@@ -7019,10 +7019,10 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>83681.58</v>
+        <v>91145.87</v>
       </c>
       <c r="I165" t="n">
-        <v>81300.08</v>
+        <v>93443.00999999999</v>
       </c>
       <c r="J165" t="n">
         <v>9</v>
@@ -7059,10 +7059,10 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>88523.85000000001</v>
+        <v>82041.53</v>
       </c>
       <c r="I166" t="n">
-        <v>87929</v>
+        <v>81485.00999999999</v>
       </c>
       <c r="J166" t="n">
         <v>6</v>
@@ -7099,10 +7099,10 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>219939.08</v>
+        <v>211412.72</v>
       </c>
       <c r="I167" t="n">
-        <v>185627.39</v>
+        <v>178887.29</v>
       </c>
       <c r="J167" t="n">
         <v>22</v>
@@ -7139,10 +7139,10 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>198618.68</v>
+        <v>194023.5</v>
       </c>
       <c r="I168" t="n">
-        <v>168417.38</v>
+        <v>164641.68</v>
       </c>
       <c r="J168" t="n">
         <v>13</v>
@@ -7179,10 +7179,10 @@
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>224416.88</v>
+        <v>203247.69</v>
       </c>
       <c r="I169" t="n">
-        <v>190181.04</v>
+        <v>171233.09</v>
       </c>
       <c r="J169" t="n">
         <v>9</v>
@@ -7219,10 +7219,10 @@
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>104959.37</v>
+        <v>89261.5</v>
       </c>
       <c r="I170" t="n">
-        <v>89970.32000000001</v>
+        <v>91468.28</v>
       </c>
       <c r="J170" t="n">
         <v>11</v>
@@ -7259,10 +7259,10 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>96108</v>
+        <v>86820.17999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>97033.47</v>
+        <v>87283.56</v>
       </c>
       <c r="J171" t="n">
         <v>6</v>
@@ -7299,10 +7299,10 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>97490.88</v>
+        <v>98424.28</v>
       </c>
       <c r="I172" t="n">
-        <v>95199.12</v>
+        <v>96407.11</v>
       </c>
       <c r="J172" t="n">
         <v>4</v>
@@ -7336,13 +7336,13 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>388915.5</v>
+        <v>368417.51</v>
       </c>
       <c r="H173" t="n">
-        <v>68186.00999999999</v>
+        <v>67901.71000000001</v>
       </c>
       <c r="I173" t="n">
-        <v>68973.3</v>
+        <v>69501.47</v>
       </c>
       <c r="J173" t="n">
         <v>19</v>
@@ -7376,13 +7376,13 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>227659.88</v>
+        <v>220500.75</v>
       </c>
       <c r="H174" t="n">
-        <v>73104.33</v>
+        <v>79165.28999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>71669.89999999999</v>
+        <v>79387.07000000001</v>
       </c>
       <c r="J174" t="n">
         <v>11</v>
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>143741.24</v>
+        <v>142356.69</v>
       </c>
       <c r="H175" t="n">
-        <v>67230.39999999999</v>
+        <v>74117.42</v>
       </c>
       <c r="I175" t="n">
-        <v>68055.08</v>
+        <v>74187.06</v>
       </c>
       <c r="J175" t="n">
         <v>7</v>
@@ -7459,10 +7459,10 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>55515.2</v>
+        <v>55327.87</v>
       </c>
       <c r="I176" t="n">
-        <v>55422.05</v>
+        <v>55239.61</v>
       </c>
       <c r="J176" t="n">
         <v>7</v>
@@ -7499,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>55987.87</v>
+        <v>56919.54</v>
       </c>
       <c r="I177" t="n">
-        <v>55957.63</v>
+        <v>57359.33</v>
       </c>
       <c r="J177" t="n">
         <v>4</v>
@@ -7539,10 +7539,10 @@
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>52918.94</v>
+        <v>56884.83</v>
       </c>
       <c r="I178" t="n">
-        <v>53465.89</v>
+        <v>55443.99</v>
       </c>
       <c r="J178" t="n">
         <v>3</v>
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>82115.11</v>
+        <v>85712.07000000001</v>
       </c>
       <c r="I179" t="n">
-        <v>81572.75999999999</v>
+        <v>86095.14</v>
       </c>
       <c r="J179" t="n">
         <v>15</v>
@@ -7619,10 +7619,10 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>89413.64</v>
+        <v>79189.87</v>
       </c>
       <c r="I180" t="n">
-        <v>90749.64999999999</v>
+        <v>79171.96000000001</v>
       </c>
       <c r="J180" t="n">
         <v>9</v>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>75640.44</v>
+        <v>94660.64999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>75927.58</v>
+        <v>93957.73</v>
       </c>
       <c r="J181" t="n">
         <v>6</v>
@@ -7699,10 +7699,10 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>205718.07</v>
+        <v>201334.72</v>
       </c>
       <c r="I182" t="n">
-        <v>173177.15</v>
+        <v>169742.32</v>
       </c>
       <c r="J182" t="n">
         <v>23</v>
@@ -7739,10 +7739,10 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>216756.61</v>
+        <v>214628.08</v>
       </c>
       <c r="I183" t="n">
-        <v>183724.48</v>
+        <v>180899.76</v>
       </c>
       <c r="J183" t="n">
         <v>13</v>
@@ -7779,10 +7779,10 @@
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>212349.83</v>
+        <v>229292.82</v>
       </c>
       <c r="I184" t="n">
-        <v>179943.05</v>
+        <v>193787.44</v>
       </c>
       <c r="J184" t="n">
         <v>9</v>
@@ -7819,10 +7819,10 @@
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>112505.05</v>
+        <v>105752.4</v>
       </c>
       <c r="I185" t="n">
-        <v>91066.67</v>
+        <v>106691.76</v>
       </c>
       <c r="J185" t="n">
         <v>11</v>
@@ -7859,10 +7859,10 @@
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>101563.81</v>
+        <v>89353.67</v>
       </c>
       <c r="I186" t="n">
-        <v>98188.3</v>
+        <v>90066.72</v>
       </c>
       <c r="J186" t="n">
         <v>6</v>
@@ -7899,10 +7899,10 @@
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>101266</v>
+        <v>154985.21</v>
       </c>
       <c r="I187" t="n">
-        <v>86752.91</v>
+        <v>100436.77</v>
       </c>
       <c r="J187" t="n">
         <v>4</v>
@@ -7936,13 +7936,13 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>235892.89</v>
+        <v>231900.28</v>
       </c>
       <c r="H188" t="n">
-        <v>70261.14999999999</v>
+        <v>77494.22</v>
       </c>
       <c r="I188" t="n">
-        <v>69732.69</v>
+        <v>77970.24000000001</v>
       </c>
       <c r="J188" t="n">
         <v>19</v>
@@ -7976,13 +7976,13 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>147888.98</v>
+        <v>152504.54</v>
       </c>
       <c r="H189" t="n">
-        <v>60085.08</v>
+        <v>80740.52</v>
       </c>
       <c r="I189" t="n">
-        <v>60486.43</v>
+        <v>79873.19</v>
       </c>
       <c r="J189" t="n">
         <v>11</v>
@@ -8016,13 +8016,13 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>102847.61</v>
+        <v>99626.49000000001</v>
       </c>
       <c r="H190" t="n">
-        <v>77184.67999999999</v>
+        <v>75624.00999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>77915.39</v>
+        <v>75222.89999999999</v>
       </c>
       <c r="J190" t="n">
         <v>7</v>
@@ -8059,10 +8059,10 @@
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>55087.09</v>
+        <v>56368.47</v>
       </c>
       <c r="I191" t="n">
-        <v>54305.25</v>
+        <v>56253.96</v>
       </c>
       <c r="J191" t="n">
         <v>7</v>
@@ -8099,10 +8099,10 @@
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>52385.83</v>
+        <v>53117.54</v>
       </c>
       <c r="I192" t="n">
-        <v>52134.02</v>
+        <v>52469.24</v>
       </c>
       <c r="J192" t="n">
         <v>4</v>
@@ -8139,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>61470.04</v>
+        <v>52531.95</v>
       </c>
       <c r="I193" t="n">
-        <v>60584.75</v>
+        <v>52308.14</v>
       </c>
       <c r="J193" t="n">
         <v>3</v>
@@ -8179,10 +8179,10 @@
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>83107.28</v>
+        <v>81593.64999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>83674.31</v>
+        <v>81067.02</v>
       </c>
       <c r="J194" t="n">
         <v>15</v>
@@ -8219,10 +8219,10 @@
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>83116.27</v>
+        <v>83674.28</v>
       </c>
       <c r="I195" t="n">
-        <v>82099.39999999999</v>
+        <v>84255.14999999999</v>
       </c>
       <c r="J195" t="n">
         <v>9</v>
@@ -8259,10 +8259,10 @@
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>86110.46000000001</v>
+        <v>88915.63</v>
       </c>
       <c r="I196" t="n">
-        <v>86239.42</v>
+        <v>88004.92999999999</v>
       </c>
       <c r="J196" t="n">
         <v>6</v>
@@ -8299,10 +8299,10 @@
         <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>217503.78</v>
+        <v>211639.73</v>
       </c>
       <c r="I197" t="n">
-        <v>184646.46</v>
+        <v>178771.65</v>
       </c>
       <c r="J197" t="n">
         <v>23</v>
@@ -8339,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>211140.61</v>
+        <v>227960.38</v>
       </c>
       <c r="I198" t="n">
-        <v>179269.96</v>
+        <v>191982.91</v>
       </c>
       <c r="J198" t="n">
         <v>13</v>
@@ -8379,10 +8379,10 @@
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>210746.39</v>
+        <v>223890.52</v>
       </c>
       <c r="I199" t="n">
-        <v>179459.34</v>
+        <v>190092.15</v>
       </c>
       <c r="J199" t="n">
         <v>9</v>
@@ -8419,10 +8419,10 @@
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>95795.08</v>
+        <v>84073.81</v>
       </c>
       <c r="I200" t="n">
-        <v>97245.09</v>
+        <v>83920.7</v>
       </c>
       <c r="J200" t="n">
         <v>11</v>
@@ -8459,10 +8459,10 @@
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>100108.21</v>
+        <v>91757.48</v>
       </c>
       <c r="I201" t="n">
-        <v>99431.02</v>
+        <v>93024.25999999999</v>
       </c>
       <c r="J201" t="n">
         <v>6</v>
@@ -8499,10 +8499,10 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>109742.54</v>
+        <v>80716.21000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>92728.92999999999</v>
+        <v>82244.36</v>
       </c>
       <c r="J202" t="n">
         <v>4</v>
@@ -8536,13 +8536,13 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>230151.51</v>
+        <v>249615.21</v>
       </c>
       <c r="H203" t="n">
-        <v>75416.35000000001</v>
+        <v>74405.37</v>
       </c>
       <c r="I203" t="n">
-        <v>76285.46000000001</v>
+        <v>73834.58</v>
       </c>
       <c r="J203" t="n">
         <v>19</v>
@@ -8576,13 +8576,13 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>151092.97</v>
+        <v>147224.28</v>
       </c>
       <c r="H204" t="n">
-        <v>77491.22</v>
+        <v>69327.99000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>76771.53</v>
+        <v>69177.95</v>
       </c>
       <c r="J204" t="n">
         <v>11</v>
@@ -8616,13 +8616,13 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>102338.71</v>
+        <v>99353.89999999999</v>
       </c>
       <c r="H205" t="n">
-        <v>70122.53999999999</v>
+        <v>73016.14</v>
       </c>
       <c r="I205" t="n">
-        <v>69595.73</v>
+        <v>73194.78</v>
       </c>
       <c r="J205" t="n">
         <v>7</v>
@@ -8659,10 +8659,10 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>48556.1</v>
+        <v>44692.37</v>
       </c>
       <c r="I206" t="n">
-        <v>48818.12</v>
+        <v>44891.33</v>
       </c>
       <c r="J206" t="n">
         <v>7</v>
@@ -8699,10 +8699,10 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>56101.08</v>
+        <v>61307.02</v>
       </c>
       <c r="I207" t="n">
-        <v>56418.07</v>
+        <v>60644.03</v>
       </c>
       <c r="J207" t="n">
         <v>4</v>
@@ -8739,10 +8739,10 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>56382.18</v>
+        <v>57479.48</v>
       </c>
       <c r="I208" t="n">
-        <v>56232.54</v>
+        <v>57577.12</v>
       </c>
       <c r="J208" t="n">
         <v>3</v>
@@ -8779,10 +8779,10 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>78766.8</v>
+        <v>91274.02</v>
       </c>
       <c r="I209" t="n">
-        <v>79484.39</v>
+        <v>93003.89</v>
       </c>
       <c r="J209" t="n">
         <v>15</v>
@@ -8819,10 +8819,10 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>81728.95</v>
+        <v>76653.53999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>80459.88</v>
+        <v>76228.46000000001</v>
       </c>
       <c r="J210" t="n">
         <v>9</v>
@@ -8859,10 +8859,10 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>80634.10000000001</v>
+        <v>84250.60000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>81685.14999999999</v>
+        <v>82981.22</v>
       </c>
       <c r="J211" t="n">
         <v>6</v>
@@ -8899,10 +8899,10 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>206699.62</v>
+        <v>213045.55</v>
       </c>
       <c r="I212" t="n">
-        <v>174571.16</v>
+        <v>178757.01</v>
       </c>
       <c r="J212" t="n">
         <v>23</v>
@@ -8939,10 +8939,10 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>216450.86</v>
+        <v>196795.1</v>
       </c>
       <c r="I213" t="n">
-        <v>181431.78</v>
+        <v>166710.67</v>
       </c>
       <c r="J213" t="n">
         <v>13</v>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>235522.33</v>
+        <v>201790.65</v>
       </c>
       <c r="I214" t="n">
-        <v>198338.44</v>
+        <v>170495.3</v>
       </c>
       <c r="J214" t="n">
         <v>9</v>
@@ -9019,10 +9019,10 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>89907.25</v>
+        <v>96657.00999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>88380.16</v>
+        <v>96404.03999999999</v>
       </c>
       <c r="J215" t="n">
         <v>11</v>
@@ -9059,10 +9059,10 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>98733.14</v>
+        <v>110553.59</v>
       </c>
       <c r="I216" t="n">
-        <v>97219.91</v>
+        <v>113273.93</v>
       </c>
       <c r="J216" t="n">
         <v>6</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>101385.46</v>
+        <v>88219.3</v>
       </c>
       <c r="I217" t="n">
-        <v>101711.62</v>
+        <v>86448.14999999999</v>
       </c>
       <c r="J217" t="n">
         <v>4</v>
@@ -9136,13 +9136,13 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>282638.02</v>
+        <v>265498.14</v>
       </c>
       <c r="H218" t="n">
-        <v>73485.75999999999</v>
+        <v>79189.05</v>
       </c>
       <c r="I218" t="n">
-        <v>70951.25999999999</v>
+        <v>77976.12</v>
       </c>
       <c r="J218" t="n">
         <v>19</v>
@@ -9176,13 +9176,13 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>170516.61</v>
+        <v>158393.66</v>
       </c>
       <c r="H219" t="n">
-        <v>74660.3</v>
+        <v>70268.13</v>
       </c>
       <c r="I219" t="n">
-        <v>74403.39</v>
+        <v>72857.42999999999</v>
       </c>
       <c r="J219" t="n">
         <v>11</v>
@@ -9216,13 +9216,13 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>118307.94</v>
+        <v>106879.8</v>
       </c>
       <c r="H220" t="n">
-        <v>79470.35000000001</v>
+        <v>83443.42999999999</v>
       </c>
       <c r="I220" t="n">
-        <v>79944.8</v>
+        <v>83188.5</v>
       </c>
       <c r="J220" t="n">
         <v>7</v>
@@ -9259,10 +9259,10 @@
         <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>55082.86</v>
+        <v>53887.04</v>
       </c>
       <c r="I221" t="n">
-        <v>54766.35</v>
+        <v>53919.77</v>
       </c>
       <c r="J221" t="n">
         <v>7</v>
@@ -9299,10 +9299,10 @@
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>52594.36</v>
+        <v>53913.3</v>
       </c>
       <c r="I222" t="n">
-        <v>54507.81</v>
+        <v>54553.35</v>
       </c>
       <c r="J222" t="n">
         <v>4</v>
@@ -9339,10 +9339,10 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>51460.52</v>
+        <v>54021.25</v>
       </c>
       <c r="I223" t="n">
-        <v>52658.37</v>
+        <v>55110.35</v>
       </c>
       <c r="J223" t="n">
         <v>3</v>
@@ -9379,10 +9379,10 @@
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>84132.47</v>
+        <v>88242.60000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>84616.02</v>
+        <v>87213.85000000001</v>
       </c>
       <c r="J224" t="n">
         <v>15</v>
@@ -9419,10 +9419,10 @@
         <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>85234.56</v>
+        <v>81648.07000000001</v>
       </c>
       <c r="I225" t="n">
-        <v>84911.03</v>
+        <v>80259.53999999999</v>
       </c>
       <c r="J225" t="n">
         <v>9</v>
@@ -9459,10 +9459,10 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>86406.19</v>
+        <v>79493.75</v>
       </c>
       <c r="I226" t="n">
-        <v>85205.88</v>
+        <v>80232.5</v>
       </c>
       <c r="J226" t="n">
         <v>6</v>
@@ -9499,10 +9499,10 @@
         <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>217250.32</v>
+        <v>205797.56</v>
       </c>
       <c r="I227" t="n">
-        <v>182244.49</v>
+        <v>173876</v>
       </c>
       <c r="J227" t="n">
         <v>23</v>
@@ -9539,10 +9539,10 @@
         <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>193227.59</v>
+        <v>180534.91</v>
       </c>
       <c r="I228" t="n">
-        <v>163311.16</v>
+        <v>153587.32</v>
       </c>
       <c r="J228" t="n">
         <v>13</v>
@@ -9579,10 +9579,10 @@
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>231852.83</v>
+        <v>228086.49</v>
       </c>
       <c r="I229" t="n">
-        <v>195395</v>
+        <v>192567.08</v>
       </c>
       <c r="J229" t="n">
         <v>9</v>
@@ -9619,10 +9619,10 @@
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>90937.42</v>
+        <v>124052.62</v>
       </c>
       <c r="I230" t="n">
-        <v>88303.92999999999</v>
+        <v>94902.17</v>
       </c>
       <c r="J230" t="n">
         <v>11</v>
@@ -9659,10 +9659,10 @@
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>136423.98</v>
+        <v>110141.04</v>
       </c>
       <c r="I231" t="n">
-        <v>108946.9</v>
+        <v>91823.35000000001</v>
       </c>
       <c r="J231" t="n">
         <v>6</v>
@@ -9699,10 +9699,10 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>109810.16</v>
+        <v>91968.94</v>
       </c>
       <c r="I232" t="n">
-        <v>92721.2</v>
+        <v>91282.35000000001</v>
       </c>
       <c r="J232" t="n">
         <v>4</v>
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>283145.94</v>
+        <v>262310.39</v>
       </c>
       <c r="H233" t="n">
-        <v>74382.7</v>
+        <v>76848.45</v>
       </c>
       <c r="I233" t="n">
-        <v>75749.12</v>
+        <v>79277.96000000001</v>
       </c>
       <c r="J233" t="n">
         <v>19</v>
@@ -9776,13 +9776,13 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>156283.47</v>
+        <v>165482.88</v>
       </c>
       <c r="H234" t="n">
-        <v>70963.60000000001</v>
+        <v>68478.14</v>
       </c>
       <c r="I234" t="n">
-        <v>69548.63</v>
+        <v>68774.87</v>
       </c>
       <c r="J234" t="n">
         <v>11</v>
@@ -9816,13 +9816,13 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>117189.37</v>
+        <v>112726.96</v>
       </c>
       <c r="H235" t="n">
-        <v>67765.86</v>
+        <v>72672.41</v>
       </c>
       <c r="I235" t="n">
-        <v>67327.95</v>
+        <v>70987.19</v>
       </c>
       <c r="J235" t="n">
         <v>7</v>
@@ -9859,10 +9859,10 @@
         <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>51272.77</v>
+        <v>59688.69</v>
       </c>
       <c r="I236" t="n">
-        <v>51203.29</v>
+        <v>59276.49</v>
       </c>
       <c r="J236" t="n">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>54837.95</v>
+        <v>56237.41</v>
       </c>
       <c r="I237" t="n">
-        <v>55159.7</v>
+        <v>56403.27</v>
       </c>
       <c r="J237" t="n">
         <v>4</v>
@@ -9939,10 +9939,10 @@
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>53111.89</v>
+        <v>46626.27</v>
       </c>
       <c r="I238" t="n">
-        <v>52284.95</v>
+        <v>47819.44</v>
       </c>
       <c r="J238" t="n">
         <v>3</v>
@@ -9979,10 +9979,10 @@
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>85258.96000000001</v>
+        <v>85409.59</v>
       </c>
       <c r="I239" t="n">
-        <v>83271.81</v>
+        <v>84320.44</v>
       </c>
       <c r="J239" t="n">
         <v>15</v>
@@ -10019,10 +10019,10 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>88497.39</v>
+        <v>80572.42999999999</v>
       </c>
       <c r="I240" t="n">
-        <v>86844.64999999999</v>
+        <v>81152.94</v>
       </c>
       <c r="J240" t="n">
         <v>9</v>
@@ -10059,10 +10059,10 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>86736.58</v>
+        <v>87571.02</v>
       </c>
       <c r="I241" t="n">
-        <v>86286.5</v>
+        <v>88894.09</v>
       </c>
       <c r="J241" t="n">
         <v>6</v>
@@ -10099,10 +10099,10 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>223024.53</v>
+        <v>213923.03</v>
       </c>
       <c r="I242" t="n">
-        <v>187963.58</v>
+        <v>180245.07</v>
       </c>
       <c r="J242" t="n">
         <v>23</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>220716.52</v>
+        <v>228636.35</v>
       </c>
       <c r="I243" t="n">
-        <v>186189.47</v>
+        <v>193665.38</v>
       </c>
       <c r="J243" t="n">
         <v>13</v>
@@ -10179,10 +10179,10 @@
         <v>0</v>
       </c>
       <c r="H244" t="n">
-        <v>229511.44</v>
+        <v>217329.43</v>
       </c>
       <c r="I244" t="n">
-        <v>192126.06</v>
+        <v>182338.34</v>
       </c>
       <c r="J244" t="n">
         <v>9</v>
@@ -10219,10 +10219,10 @@
         <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>92202.95</v>
+        <v>111616.56</v>
       </c>
       <c r="I245" t="n">
-        <v>90058.47</v>
+        <v>112511.81</v>
       </c>
       <c r="J245" t="n">
         <v>11</v>
@@ -10259,10 +10259,10 @@
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>96146.63</v>
+        <v>91690.89999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>95351.03999999999</v>
+        <v>91301.97</v>
       </c>
       <c r="J246" t="n">
         <v>6</v>
@@ -10299,10 +10299,10 @@
         <v>0</v>
       </c>
       <c r="H247" t="n">
-        <v>111712.24</v>
+        <v>94691.92999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>90427.19</v>
+        <v>95927.8</v>
       </c>
       <c r="J247" t="n">
         <v>4</v>
@@ -10336,13 +10336,13 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>291904.95</v>
+        <v>260640.39</v>
       </c>
       <c r="H248" t="n">
-        <v>74864.07000000001</v>
+        <v>79423.64999999999</v>
       </c>
       <c r="I248" t="n">
-        <v>75468.84</v>
+        <v>79420.88</v>
       </c>
       <c r="J248" t="n">
         <v>19</v>
@@ -10376,13 +10376,13 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>173162.9</v>
+        <v>175303.77</v>
       </c>
       <c r="H249" t="n">
-        <v>74264.72</v>
+        <v>68756.81</v>
       </c>
       <c r="I249" t="n">
-        <v>74694.89</v>
+        <v>68353.81</v>
       </c>
       <c r="J249" t="n">
         <v>11</v>
@@ -10416,13 +10416,13 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>114086.27</v>
+        <v>104347.82</v>
       </c>
       <c r="H250" t="n">
-        <v>74245.00999999999</v>
+        <v>66312.21000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>74366.55</v>
+        <v>66470.71000000001</v>
       </c>
       <c r="J250" t="n">
         <v>7</v>
@@ -10459,10 +10459,10 @@
         <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>54600.05</v>
+        <v>55326.35</v>
       </c>
       <c r="I251" t="n">
-        <v>53483.56</v>
+        <v>55363.07</v>
       </c>
       <c r="J251" t="n">
         <v>7</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>54581.81</v>
+        <v>56332.9</v>
       </c>
       <c r="I252" t="n">
-        <v>55676.61</v>
+        <v>57618.45</v>
       </c>
       <c r="J252" t="n">
         <v>4</v>
@@ -10539,10 +10539,10 @@
         <v>0</v>
       </c>
       <c r="H253" t="n">
-        <v>56313.49</v>
+        <v>49645.28</v>
       </c>
       <c r="I253" t="n">
-        <v>55776.28</v>
+        <v>47780.55</v>
       </c>
       <c r="J253" t="n">
         <v>3</v>
@@ -10579,10 +10579,10 @@
         <v>0</v>
       </c>
       <c r="H254" t="n">
-        <v>83187.22</v>
+        <v>88576.21000000001</v>
       </c>
       <c r="I254" t="n">
-        <v>83305.07000000001</v>
+        <v>88376.11</v>
       </c>
       <c r="J254" t="n">
         <v>15</v>
@@ -10619,10 +10619,10 @@
         <v>0</v>
       </c>
       <c r="H255" t="n">
-        <v>76434.84</v>
+        <v>76926.64999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>77802.39999999999</v>
+        <v>79789.74000000001</v>
       </c>
       <c r="J255" t="n">
         <v>9</v>
@@ -10659,10 +10659,10 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>85939.78999999999</v>
+        <v>82879.75999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>84985.88</v>
+        <v>79437</v>
       </c>
       <c r="J256" t="n">
         <v>6</v>
@@ -10699,10 +10699,10 @@
         <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>200884.02</v>
+        <v>225357.33</v>
       </c>
       <c r="I257" t="n">
-        <v>167418.11</v>
+        <v>190848.68</v>
       </c>
       <c r="J257" t="n">
         <v>23</v>
@@ -10739,10 +10739,10 @@
         <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>222380.15</v>
+        <v>214014.52</v>
       </c>
       <c r="I258" t="n">
-        <v>187154.76</v>
+        <v>180418.17</v>
       </c>
       <c r="J258" t="n">
         <v>13</v>
@@ -10779,10 +10779,10 @@
         <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>199309.37</v>
+        <v>194535.33</v>
       </c>
       <c r="I259" t="n">
-        <v>167900.67</v>
+        <v>164600.35</v>
       </c>
       <c r="J259" t="n">
         <v>9</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="H260" t="n">
-        <v>98513.50999999999</v>
+        <v>98403.94</v>
       </c>
       <c r="I260" t="n">
-        <v>98635.49000000001</v>
+        <v>96692.64</v>
       </c>
       <c r="J260" t="n">
         <v>11</v>
@@ -10859,10 +10859,10 @@
         <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>104612.17</v>
+        <v>104460.23</v>
       </c>
       <c r="I261" t="n">
-        <v>107204.15</v>
+        <v>103710.5</v>
       </c>
       <c r="J261" t="n">
         <v>6</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="H262" t="n">
-        <v>106089.05</v>
+        <v>91847.28</v>
       </c>
       <c r="I262" t="n">
-        <v>104837.03</v>
+        <v>93739.67999999999</v>
       </c>
       <c r="J262" t="n">
         <v>4</v>
@@ -10936,13 +10936,13 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>302676.58</v>
+        <v>304434.97</v>
       </c>
       <c r="H263" t="n">
-        <v>80950.52</v>
+        <v>70142.92999999999</v>
       </c>
       <c r="I263" t="n">
-        <v>81188.03</v>
+        <v>69985.74000000001</v>
       </c>
       <c r="J263" t="n">
         <v>19</v>
@@ -10976,13 +10976,13 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>160132.68</v>
+        <v>175136.04</v>
       </c>
       <c r="H264" t="n">
-        <v>73806.39</v>
+        <v>71415.64999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>72189.8</v>
+        <v>72448.12</v>
       </c>
       <c r="J264" t="n">
         <v>11</v>
@@ -11016,13 +11016,13 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>105584.31</v>
+        <v>108120.57</v>
       </c>
       <c r="H265" t="n">
-        <v>76907.57000000001</v>
+        <v>77579.92</v>
       </c>
       <c r="I265" t="n">
-        <v>77480.78</v>
+        <v>77728.89999999999</v>
       </c>
       <c r="J265" t="n">
         <v>7</v>
@@ -11059,10 +11059,10 @@
         <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>50334.99</v>
+        <v>53038.67</v>
       </c>
       <c r="I266" t="n">
-        <v>50977.27</v>
+        <v>52953.87</v>
       </c>
       <c r="J266" t="n">
         <v>7</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>49715.38</v>
+        <v>53923.31</v>
       </c>
       <c r="I267" t="n">
-        <v>49348.5</v>
+        <v>53694.74</v>
       </c>
       <c r="J267" t="n">
         <v>4</v>
@@ -11139,10 +11139,10 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>61719.58</v>
+        <v>55446.37</v>
       </c>
       <c r="I268" t="n">
-        <v>60692.5</v>
+        <v>54390.35</v>
       </c>
       <c r="J268" t="n">
         <v>3</v>
@@ -11179,10 +11179,10 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>82379.10000000001</v>
+        <v>81602.3</v>
       </c>
       <c r="I269" t="n">
-        <v>80758.34</v>
+        <v>79313.2</v>
       </c>
       <c r="J269" t="n">
         <v>15</v>
@@ -11219,10 +11219,10 @@
         <v>0</v>
       </c>
       <c r="H270" t="n">
-        <v>85422.98</v>
+        <v>78559.48</v>
       </c>
       <c r="I270" t="n">
-        <v>84293</v>
+        <v>78008.03</v>
       </c>
       <c r="J270" t="n">
         <v>9</v>
@@ -11259,10 +11259,10 @@
         <v>0</v>
       </c>
       <c r="H271" t="n">
-        <v>87463.75</v>
+        <v>90071.36</v>
       </c>
       <c r="I271" t="n">
-        <v>85502.5</v>
+        <v>87541.17999999999</v>
       </c>
       <c r="J271" t="n">
         <v>6</v>
@@ -11299,10 +11299,10 @@
         <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>232594.42</v>
+        <v>225871.69</v>
       </c>
       <c r="I272" t="n">
-        <v>195882.19</v>
+        <v>190894.76</v>
       </c>
       <c r="J272" t="n">
         <v>23</v>
@@ -11339,10 +11339,10 @@
         <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>199761.78</v>
+        <v>208791.02</v>
       </c>
       <c r="I273" t="n">
-        <v>168503.9</v>
+        <v>176259.4</v>
       </c>
       <c r="J273" t="n">
         <v>13</v>
@@ -11379,10 +11379,10 @@
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>201328.77</v>
+        <v>208305.79</v>
       </c>
       <c r="I274" t="n">
-        <v>169221.17</v>
+        <v>176439.8</v>
       </c>
       <c r="J274" t="n">
         <v>9</v>
@@ -11419,10 +11419,10 @@
         <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>127146.62</v>
+        <v>88976.34</v>
       </c>
       <c r="I275" t="n">
-        <v>90646.85000000001</v>
+        <v>87761.71000000001</v>
       </c>
       <c r="J275" t="n">
         <v>11</v>
@@ -11459,10 +11459,10 @@
         <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>101954.8</v>
+        <v>108955.18</v>
       </c>
       <c r="I276" t="n">
-        <v>102344.17</v>
+        <v>92272.34</v>
       </c>
       <c r="J276" t="n">
         <v>6</v>
@@ -11499,10 +11499,10 @@
         <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>95679.35000000001</v>
+        <v>129239.25</v>
       </c>
       <c r="I277" t="n">
-        <v>95639.66</v>
+        <v>99232.58</v>
       </c>
       <c r="J277" t="n">
         <v>4</v>
@@ -11536,13 +11536,13 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>270637.6</v>
+        <v>270013.56</v>
       </c>
       <c r="H278" t="n">
-        <v>68050.89999999999</v>
+        <v>69670.53999999999</v>
       </c>
       <c r="I278" t="n">
-        <v>67047.24000000001</v>
+        <v>69160.74000000001</v>
       </c>
       <c r="J278" t="n">
         <v>19</v>
@@ -11576,13 +11576,13 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>170605.41</v>
+        <v>159105.82</v>
       </c>
       <c r="H279" t="n">
-        <v>74051.08</v>
+        <v>80672.64999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>75432.98</v>
+        <v>81922.84</v>
       </c>
       <c r="J279" t="n">
         <v>11</v>
@@ -11616,13 +11616,13 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>116754.42</v>
+        <v>108815.85</v>
       </c>
       <c r="H280" t="n">
-        <v>75110.05</v>
+        <v>81429.75</v>
       </c>
       <c r="I280" t="n">
-        <v>73936.32000000001</v>
+        <v>81948.19</v>
       </c>
       <c r="J280" t="n">
         <v>7</v>
@@ -11659,10 +11659,10 @@
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>51817.93</v>
+        <v>60596.42</v>
       </c>
       <c r="I281" t="n">
-        <v>50868.66</v>
+        <v>61014.96</v>
       </c>
       <c r="J281" t="n">
         <v>7</v>
@@ -11699,10 +11699,10 @@
         <v>0</v>
       </c>
       <c r="H282" t="n">
-        <v>55461.45</v>
+        <v>43698.15</v>
       </c>
       <c r="I282" t="n">
-        <v>56343.7</v>
+        <v>43446.26</v>
       </c>
       <c r="J282" t="n">
         <v>4</v>
@@ -11739,10 +11739,10 @@
         <v>0</v>
       </c>
       <c r="H283" t="n">
-        <v>55975.83</v>
+        <v>50000.34</v>
       </c>
       <c r="I283" t="n">
-        <v>55913.16</v>
+        <v>50552.3</v>
       </c>
       <c r="J283" t="n">
         <v>3</v>
@@ -11779,10 +11779,10 @@
         <v>0</v>
       </c>
       <c r="H284" t="n">
-        <v>81596.02</v>
+        <v>91173.66</v>
       </c>
       <c r="I284" t="n">
-        <v>80253.55</v>
+        <v>93087.44</v>
       </c>
       <c r="J284" t="n">
         <v>15</v>
@@ -11819,10 +11819,10 @@
         <v>0</v>
       </c>
       <c r="H285" t="n">
-        <v>79026.36</v>
+        <v>84543.23</v>
       </c>
       <c r="I285" t="n">
-        <v>78633.2</v>
+        <v>84149.82000000001</v>
       </c>
       <c r="J285" t="n">
         <v>9</v>
@@ -11859,10 +11859,10 @@
         <v>0</v>
       </c>
       <c r="H286" t="n">
-        <v>90589.87</v>
+        <v>87211.12</v>
       </c>
       <c r="I286" t="n">
-        <v>90996.42</v>
+        <v>86088.78</v>
       </c>
       <c r="J286" t="n">
         <v>6</v>
@@ -11899,10 +11899,10 @@
         <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>234399.31</v>
+        <v>220404.33</v>
       </c>
       <c r="I287" t="n">
-        <v>197207.17</v>
+        <v>186740.79</v>
       </c>
       <c r="J287" t="n">
         <v>23</v>
@@ -11939,10 +11939,10 @@
         <v>0</v>
       </c>
       <c r="H288" t="n">
-        <v>212705.86</v>
+        <v>218967.05</v>
       </c>
       <c r="I288" t="n">
-        <v>178906.96</v>
+        <v>183720.12</v>
       </c>
       <c r="J288" t="n">
         <v>13</v>
@@ -11979,10 +11979,10 @@
         <v>0</v>
       </c>
       <c r="H289" t="n">
-        <v>188427.91</v>
+        <v>206354.79</v>
       </c>
       <c r="I289" t="n">
-        <v>158925.86</v>
+        <v>173801.88</v>
       </c>
       <c r="J289" t="n">
         <v>9</v>
@@ -12019,10 +12019,10 @@
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>88052.50999999999</v>
+        <v>113457.78</v>
       </c>
       <c r="I290" t="n">
-        <v>88186.66</v>
+        <v>93106.41</v>
       </c>
       <c r="J290" t="n">
         <v>11</v>
@@ -12059,10 +12059,10 @@
         <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>115892.35</v>
+        <v>98416.72</v>
       </c>
       <c r="I291" t="n">
-        <v>98402.22</v>
+        <v>98218.5</v>
       </c>
       <c r="J291" t="n">
         <v>6</v>
@@ -12099,10 +12099,10 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>114762.97</v>
+        <v>92215.24000000001</v>
       </c>
       <c r="I292" t="n">
-        <v>94682.61</v>
+        <v>92038.36</v>
       </c>
       <c r="J292" t="n">
         <v>4</v>
@@ -12136,13 +12136,13 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>285562.46</v>
+        <v>258681.2</v>
       </c>
       <c r="H293" t="n">
-        <v>75421.06</v>
+        <v>70120.91</v>
       </c>
       <c r="I293" t="n">
-        <v>75412.2</v>
+        <v>69922.64999999999</v>
       </c>
       <c r="J293" t="n">
         <v>19</v>
@@ -12176,13 +12176,13 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>167444.01</v>
+        <v>167880.74</v>
       </c>
       <c r="H294" t="n">
-        <v>77997.58</v>
+        <v>77355.06</v>
       </c>
       <c r="I294" t="n">
-        <v>79381.09</v>
+        <v>79193.78999999999</v>
       </c>
       <c r="J294" t="n">
         <v>11</v>
@@ -12216,13 +12216,13 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>103431.8</v>
+        <v>111228.2</v>
       </c>
       <c r="H295" t="n">
-        <v>69478.96000000001</v>
+        <v>72541.38</v>
       </c>
       <c r="I295" t="n">
-        <v>68309.97</v>
+        <v>70452.64</v>
       </c>
       <c r="J295" t="n">
         <v>7</v>
@@ -12259,10 +12259,10 @@
         <v>0</v>
       </c>
       <c r="H296" t="n">
-        <v>53231.49</v>
+        <v>52705.99</v>
       </c>
       <c r="I296" t="n">
-        <v>54144.73</v>
+        <v>52806.33</v>
       </c>
       <c r="J296" t="n">
         <v>7</v>
@@ -12299,10 +12299,10 @@
         <v>0</v>
       </c>
       <c r="H297" t="n">
-        <v>54724.15</v>
+        <v>47986.3</v>
       </c>
       <c r="I297" t="n">
-        <v>54024.47</v>
+        <v>47789.88</v>
       </c>
       <c r="J297" t="n">
         <v>4</v>
@@ -12339,10 +12339,10 @@
         <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>51502.01</v>
+        <v>52741.42</v>
       </c>
       <c r="I298" t="n">
-        <v>52431.47</v>
+        <v>53431.42</v>
       </c>
       <c r="J298" t="n">
         <v>3</v>
@@ -12379,10 +12379,10 @@
         <v>0</v>
       </c>
       <c r="H299" t="n">
-        <v>97827.32000000001</v>
+        <v>89927.82000000001</v>
       </c>
       <c r="I299" t="n">
-        <v>96423.36</v>
+        <v>87713.5</v>
       </c>
       <c r="J299" t="n">
         <v>15</v>
@@ -12419,10 +12419,10 @@
         <v>0</v>
       </c>
       <c r="H300" t="n">
-        <v>83592.7</v>
+        <v>86596.57000000001</v>
       </c>
       <c r="I300" t="n">
-        <v>85090.41</v>
+        <v>88129.64999999999</v>
       </c>
       <c r="J300" t="n">
         <v>9</v>
@@ -12459,10 +12459,10 @@
         <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>87895.73</v>
+        <v>81141.82000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>85662.99000000001</v>
+        <v>81832.92</v>
       </c>
       <c r="J301" t="n">
         <v>6</v>
@@ -12499,10 +12499,10 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>226032.09</v>
+        <v>189541.07</v>
       </c>
       <c r="I302" t="n">
-        <v>190659.15</v>
+        <v>159494.15</v>
       </c>
       <c r="J302" t="n">
         <v>23</v>
@@ -12539,10 +12539,10 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>210718.15</v>
+        <v>213312.11</v>
       </c>
       <c r="I303" t="n">
-        <v>177304.4</v>
+        <v>178986.34</v>
       </c>
       <c r="J303" t="n">
         <v>13</v>
@@ -12579,10 +12579,10 @@
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>210510.58</v>
+        <v>223419.89</v>
       </c>
       <c r="I304" t="n">
-        <v>177478.64</v>
+        <v>188805.21</v>
       </c>
       <c r="J304" t="n">
         <v>9</v>
@@ -12619,10 +12619,10 @@
         <v>0</v>
       </c>
       <c r="H305" t="n">
-        <v>90559.66</v>
+        <v>101586.21</v>
       </c>
       <c r="I305" t="n">
-        <v>91077.74000000001</v>
+        <v>102600.99</v>
       </c>
       <c r="J305" t="n">
         <v>11</v>
@@ -12659,10 +12659,10 @@
         <v>0</v>
       </c>
       <c r="H306" t="n">
-        <v>93178.02</v>
+        <v>99909.62</v>
       </c>
       <c r="I306" t="n">
-        <v>92429.42</v>
+        <v>100266.52</v>
       </c>
       <c r="J306" t="n">
         <v>6</v>
@@ -12699,10 +12699,10 @@
         <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>92548.5</v>
+        <v>90326.84</v>
       </c>
       <c r="I307" t="n">
-        <v>92048.77</v>
+        <v>92605.77</v>
       </c>
       <c r="J307" t="n">
         <v>4</v>
@@ -12736,13 +12736,13 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>258469.11</v>
+        <v>262269.33</v>
       </c>
       <c r="H308" t="n">
-        <v>75833.13</v>
+        <v>82562.71000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>76435.21000000001</v>
+        <v>83586.48</v>
       </c>
       <c r="J308" t="n">
         <v>19</v>
@@ -12776,13 +12776,13 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>170037.43</v>
+        <v>172066.67</v>
       </c>
       <c r="H309" t="n">
-        <v>71545.96000000001</v>
+        <v>73412.75</v>
       </c>
       <c r="I309" t="n">
-        <v>71121.21000000001</v>
+        <v>72199.57000000001</v>
       </c>
       <c r="J309" t="n">
         <v>11</v>
@@ -12816,13 +12816,13 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>117788.47</v>
+        <v>108768.52</v>
       </c>
       <c r="H310" t="n">
-        <v>73297.72</v>
+        <v>73127.98</v>
       </c>
       <c r="I310" t="n">
-        <v>72348.09</v>
+        <v>73457.50999999999</v>
       </c>
       <c r="J310" t="n">
         <v>7</v>
@@ -12859,10 +12859,10 @@
         <v>0</v>
       </c>
       <c r="H311" t="n">
-        <v>53022.64</v>
+        <v>52949.32</v>
       </c>
       <c r="I311" t="n">
-        <v>52532.99</v>
+        <v>53322.74</v>
       </c>
       <c r="J311" t="n">
         <v>7</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="H312" t="n">
-        <v>57122.87</v>
+        <v>56852.48</v>
       </c>
       <c r="I312" t="n">
-        <v>56848.06</v>
+        <v>57186.36</v>
       </c>
       <c r="J312" t="n">
         <v>4</v>
@@ -12939,10 +12939,10 @@
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>52598.11</v>
+        <v>55013.23</v>
       </c>
       <c r="I313" t="n">
-        <v>52062.43</v>
+        <v>54903.84</v>
       </c>
       <c r="J313" t="n">
         <v>3</v>
@@ -12979,10 +12979,10 @@
         <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>86747.27</v>
+        <v>81504.64</v>
       </c>
       <c r="I314" t="n">
-        <v>85679.25999999999</v>
+        <v>80318.59</v>
       </c>
       <c r="J314" t="n">
         <v>15</v>
@@ -13019,10 +13019,10 @@
         <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>94133.95</v>
+        <v>88438.66</v>
       </c>
       <c r="I315" t="n">
-        <v>93804.8</v>
+        <v>90065.52</v>
       </c>
       <c r="J315" t="n">
         <v>9</v>
@@ -13059,10 +13059,10 @@
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>77881.8</v>
+        <v>86409.72</v>
       </c>
       <c r="I316" t="n">
-        <v>79761.75</v>
+        <v>87966.59</v>
       </c>
       <c r="J316" t="n">
         <v>6</v>
@@ -13099,10 +13099,10 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>218636.74</v>
+        <v>208283.83</v>
       </c>
       <c r="I317" t="n">
-        <v>185175.85</v>
+        <v>175548.38</v>
       </c>
       <c r="J317" t="n">
         <v>23</v>
@@ -13139,10 +13139,10 @@
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>204986.27</v>
+        <v>214159.55</v>
       </c>
       <c r="I318" t="n">
-        <v>173368.06</v>
+        <v>180668.25</v>
       </c>
       <c r="J318" t="n">
         <v>13</v>
@@ -13179,10 +13179,10 @@
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>212679.46</v>
+        <v>209866.52</v>
       </c>
       <c r="I319" t="n">
-        <v>179231.12</v>
+        <v>177359.9</v>
       </c>
       <c r="J319" t="n">
         <v>9</v>
@@ -13219,10 +13219,10 @@
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>131038.79</v>
+        <v>90273.27</v>
       </c>
       <c r="I320" t="n">
-        <v>98975.33</v>
+        <v>90614.49000000001</v>
       </c>
       <c r="J320" t="n">
         <v>11</v>
@@ -13259,10 +13259,10 @@
         <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>98445.10000000001</v>
+        <v>119683.77</v>
       </c>
       <c r="I321" t="n">
-        <v>100339.56</v>
+        <v>93236.39999999999</v>
       </c>
       <c r="J321" t="n">
         <v>6</v>
@@ -13299,10 +13299,10 @@
         <v>0</v>
       </c>
       <c r="H322" t="n">
-        <v>98945.78</v>
+        <v>104013.57</v>
       </c>
       <c r="I322" t="n">
-        <v>98386.24000000001</v>
+        <v>103524.96</v>
       </c>
       <c r="J322" t="n">
         <v>4</v>
@@ -13336,13 +13336,13 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>409105.22</v>
+        <v>432161.31</v>
       </c>
       <c r="H323" t="n">
-        <v>74831.83</v>
+        <v>76932.89999999999</v>
       </c>
       <c r="I323" t="n">
-        <v>75520.16</v>
+        <v>75144.53999999999</v>
       </c>
       <c r="J323" t="n">
         <v>19</v>
@@ -13376,13 +13376,13 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>246704.18</v>
+        <v>242178.67</v>
       </c>
       <c r="H324" t="n">
-        <v>78012.56</v>
+        <v>69397.32000000001</v>
       </c>
       <c r="I324" t="n">
-        <v>79254.22</v>
+        <v>70086.05</v>
       </c>
       <c r="J324" t="n">
         <v>11</v>
@@ -13416,13 +13416,13 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>163603.25</v>
+        <v>166622.45</v>
       </c>
       <c r="H325" t="n">
-        <v>73712.28</v>
+        <v>72797.27</v>
       </c>
       <c r="I325" t="n">
-        <v>73926.24000000001</v>
+        <v>73987.42</v>
       </c>
       <c r="J325" t="n">
         <v>7</v>
@@ -13459,10 +13459,10 @@
         <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>56005.81</v>
+        <v>54476.34</v>
       </c>
       <c r="I326" t="n">
-        <v>55539.1</v>
+        <v>55558.94</v>
       </c>
       <c r="J326" t="n">
         <v>7</v>
@@ -13499,10 +13499,10 @@
         <v>0</v>
       </c>
       <c r="H327" t="n">
-        <v>52392.65</v>
+        <v>51577.92</v>
       </c>
       <c r="I327" t="n">
-        <v>51048.74</v>
+        <v>52941.91</v>
       </c>
       <c r="J327" t="n">
         <v>4</v>
@@ -13539,10 +13539,10 @@
         <v>0</v>
       </c>
       <c r="H328" t="n">
-        <v>56880.2</v>
+        <v>61745.74</v>
       </c>
       <c r="I328" t="n">
-        <v>57252.3</v>
+        <v>63094.11</v>
       </c>
       <c r="J328" t="n">
         <v>3</v>
@@ -13579,10 +13579,10 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>78391.11</v>
+        <v>77729.74000000001</v>
       </c>
       <c r="I329" t="n">
-        <v>77290.99000000001</v>
+        <v>79529.78</v>
       </c>
       <c r="J329" t="n">
         <v>15</v>
@@ -13619,10 +13619,10 @@
         <v>0</v>
       </c>
       <c r="H330" t="n">
-        <v>87614.27</v>
+        <v>88813.85000000001</v>
       </c>
       <c r="I330" t="n">
-        <v>86365.74000000001</v>
+        <v>88807.96000000001</v>
       </c>
       <c r="J330" t="n">
         <v>9</v>
@@ -13659,10 +13659,10 @@
         <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>85979.53</v>
+        <v>78006.28999999999</v>
       </c>
       <c r="I331" t="n">
-        <v>85376.67999999999</v>
+        <v>77451.50999999999</v>
       </c>
       <c r="J331" t="n">
         <v>6</v>
@@ -13699,10 +13699,10 @@
         <v>0</v>
       </c>
       <c r="H332" t="n">
-        <v>204406.59</v>
+        <v>215158.72</v>
       </c>
       <c r="I332" t="n">
-        <v>171877.58</v>
+        <v>180980.19</v>
       </c>
       <c r="J332" t="n">
         <v>23</v>
@@ -13739,10 +13739,10 @@
         <v>0</v>
       </c>
       <c r="H333" t="n">
-        <v>182462.24</v>
+        <v>176199.75</v>
       </c>
       <c r="I333" t="n">
-        <v>153492.05</v>
+        <v>148070.83</v>
       </c>
       <c r="J333" t="n">
         <v>13</v>
@@ -13779,10 +13779,10 @@
         <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>204948.59</v>
+        <v>247885.81</v>
       </c>
       <c r="I334" t="n">
-        <v>173423.15</v>
+        <v>207879.02</v>
       </c>
       <c r="J334" t="n">
         <v>9</v>
@@ -13819,10 +13819,10 @@
         <v>0</v>
       </c>
       <c r="H335" t="n">
-        <v>105970.7</v>
+        <v>129034.03</v>
       </c>
       <c r="I335" t="n">
-        <v>94550.60000000001</v>
+        <v>103759.73</v>
       </c>
       <c r="J335" t="n">
         <v>11</v>
@@ -13859,10 +13859,10 @@
         <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>94282.36</v>
+        <v>95826.25999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>94739.35000000001</v>
+        <v>95855.92</v>
       </c>
       <c r="J336" t="n">
         <v>6</v>
@@ -13899,10 +13899,10 @@
         <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>88527.78999999999</v>
+        <v>104478.98</v>
       </c>
       <c r="I337" t="n">
-        <v>87410.66</v>
+        <v>103478.17</v>
       </c>
       <c r="J337" t="n">
         <v>4</v>
@@ -13936,13 +13936,13 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>410507.05</v>
+        <v>381797.23</v>
       </c>
       <c r="H338" t="n">
-        <v>77022.83</v>
+        <v>64781.11</v>
       </c>
       <c r="I338" t="n">
-        <v>77332.75</v>
+        <v>63834.33</v>
       </c>
       <c r="J338" t="n">
         <v>19</v>
@@ -13976,13 +13976,13 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>250437.78</v>
+        <v>242420.68</v>
       </c>
       <c r="H339" t="n">
-        <v>76374.83</v>
+        <v>84736.72</v>
       </c>
       <c r="I339" t="n">
-        <v>76626.12</v>
+        <v>82748.24000000001</v>
       </c>
       <c r="J339" t="n">
         <v>11</v>
@@ -14016,13 +14016,13 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>159529.2</v>
+        <v>162819.23</v>
       </c>
       <c r="H340" t="n">
-        <v>70038.08</v>
+        <v>80722.3</v>
       </c>
       <c r="I340" t="n">
-        <v>70685.28999999999</v>
+        <v>81791.41</v>
       </c>
       <c r="J340" t="n">
         <v>7</v>
@@ -14059,10 +14059,10 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>55053.57</v>
+        <v>47897.41</v>
       </c>
       <c r="I341" t="n">
-        <v>54023.88</v>
+        <v>48362.25</v>
       </c>
       <c r="J341" t="n">
         <v>7</v>
@@ -14099,10 +14099,10 @@
         <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>56489.93</v>
+        <v>58396.18</v>
       </c>
       <c r="I342" t="n">
-        <v>58158.1</v>
+        <v>56278.1</v>
       </c>
       <c r="J342" t="n">
         <v>4</v>
@@ -14139,10 +14139,10 @@
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>46124.1</v>
+        <v>51895.65</v>
       </c>
       <c r="I343" t="n">
-        <v>45214.68</v>
+        <v>51126.79</v>
       </c>
       <c r="J343" t="n">
         <v>3</v>
@@ -14179,10 +14179,10 @@
         <v>0</v>
       </c>
       <c r="H344" t="n">
-        <v>87970.63</v>
+        <v>81862.75</v>
       </c>
       <c r="I344" t="n">
-        <v>87956.12</v>
+        <v>81068.73</v>
       </c>
       <c r="J344" t="n">
         <v>15</v>
@@ -14219,10 +14219,10 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>93628.81</v>
+        <v>91286.94</v>
       </c>
       <c r="I345" t="n">
-        <v>93496.38</v>
+        <v>89755.55</v>
       </c>
       <c r="J345" t="n">
         <v>9</v>
@@ -14259,10 +14259,10 @@
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>79291.78999999999</v>
+        <v>82645.57000000001</v>
       </c>
       <c r="I346" t="n">
-        <v>78335.03</v>
+        <v>82716.36</v>
       </c>
       <c r="J346" t="n">
         <v>6</v>
@@ -14299,10 +14299,10 @@
         <v>0</v>
       </c>
       <c r="H347" t="n">
-        <v>201397.19</v>
+        <v>210760.51</v>
       </c>
       <c r="I347" t="n">
-        <v>170246.52</v>
+        <v>178010.14</v>
       </c>
       <c r="J347" t="n">
         <v>23</v>
@@ -14339,10 +14339,10 @@
         <v>0</v>
       </c>
       <c r="H348" t="n">
-        <v>204964.4</v>
+        <v>204844.82</v>
       </c>
       <c r="I348" t="n">
-        <v>173322.82</v>
+        <v>172377.19</v>
       </c>
       <c r="J348" t="n">
         <v>13</v>
@@ -14379,10 +14379,10 @@
         <v>0</v>
       </c>
       <c r="H349" t="n">
-        <v>230807.47</v>
+        <v>177492.6</v>
       </c>
       <c r="I349" t="n">
-        <v>194717.19</v>
+        <v>149708.76</v>
       </c>
       <c r="J349" t="n">
         <v>9</v>
@@ -14419,10 +14419,10 @@
         <v>0</v>
       </c>
       <c r="H350" t="n">
-        <v>125349.05</v>
+        <v>94844.64</v>
       </c>
       <c r="I350" t="n">
-        <v>97202.48</v>
+        <v>94672.25</v>
       </c>
       <c r="J350" t="n">
         <v>11</v>
@@ -14459,10 +14459,10 @@
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>93174.3</v>
+        <v>90331.57000000001</v>
       </c>
       <c r="I351" t="n">
-        <v>93663.33</v>
+        <v>89248.09</v>
       </c>
       <c r="J351" t="n">
         <v>6</v>
@@ -14499,10 +14499,10 @@
         <v>0</v>
       </c>
       <c r="H352" t="n">
-        <v>96979.94</v>
+        <v>116639.88</v>
       </c>
       <c r="I352" t="n">
-        <v>96785.98</v>
+        <v>94764.25</v>
       </c>
       <c r="J352" t="n">
         <v>4</v>
@@ -14536,13 +14536,13 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>406373.68</v>
+        <v>389130.35</v>
       </c>
       <c r="H353" t="n">
-        <v>73260.37</v>
+        <v>76014.77</v>
       </c>
       <c r="I353" t="n">
-        <v>73378.56</v>
+        <v>74478.32000000001</v>
       </c>
       <c r="J353" t="n">
         <v>19</v>
@@ -14576,13 +14576,13 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>264129.65</v>
+        <v>230798.29</v>
       </c>
       <c r="H354" t="n">
-        <v>78199.17999999999</v>
+        <v>66702.03999999999</v>
       </c>
       <c r="I354" t="n">
-        <v>78178.08</v>
+        <v>67697.02</v>
       </c>
       <c r="J354" t="n">
         <v>11</v>
@@ -14616,13 +14616,13 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>155535.14</v>
+        <v>162262.6</v>
       </c>
       <c r="H355" t="n">
-        <v>79095.89999999999</v>
+        <v>84876.8</v>
       </c>
       <c r="I355" t="n">
-        <v>77851.78999999999</v>
+        <v>84191.12</v>
       </c>
       <c r="J355" t="n">
         <v>7</v>
@@ -14659,10 +14659,10 @@
         <v>0</v>
       </c>
       <c r="H356" t="n">
-        <v>44792.37</v>
+        <v>50829.69</v>
       </c>
       <c r="I356" t="n">
-        <v>44140.71</v>
+        <v>51601.35</v>
       </c>
       <c r="J356" t="n">
         <v>7</v>
@@ -14699,10 +14699,10 @@
         <v>0</v>
       </c>
       <c r="H357" t="n">
-        <v>55582.57</v>
+        <v>48269.31</v>
       </c>
       <c r="I357" t="n">
-        <v>56966.26</v>
+        <v>48975.08</v>
       </c>
       <c r="J357" t="n">
         <v>4</v>
@@ -14739,10 +14739,10 @@
         <v>0</v>
       </c>
       <c r="H358" t="n">
-        <v>58508.28</v>
+        <v>51095.79</v>
       </c>
       <c r="I358" t="n">
-        <v>59606.21</v>
+        <v>51995.56</v>
       </c>
       <c r="J358" t="n">
         <v>3</v>
@@ -14779,10 +14779,10 @@
         <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>75904.96000000001</v>
+        <v>90228.61</v>
       </c>
       <c r="I359" t="n">
-        <v>77276.10000000001</v>
+        <v>91476.08</v>
       </c>
       <c r="J359" t="n">
         <v>15</v>
@@ -14819,10 +14819,10 @@
         <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>81696.21000000001</v>
+        <v>86845.00999999999</v>
       </c>
       <c r="I360" t="n">
-        <v>82602.5</v>
+        <v>86792.09</v>
       </c>
       <c r="J360" t="n">
         <v>9</v>
@@ -14859,10 +14859,10 @@
         <v>0</v>
       </c>
       <c r="H361" t="n">
-        <v>82206.92</v>
+        <v>87530.98</v>
       </c>
       <c r="I361" t="n">
-        <v>82360.98</v>
+        <v>86696.74000000001</v>
       </c>
       <c r="J361" t="n">
         <v>6</v>
@@ -14899,10 +14899,10 @@
         <v>0</v>
       </c>
       <c r="H362" t="n">
-        <v>203581.16</v>
+        <v>220818.04</v>
       </c>
       <c r="I362" t="n">
-        <v>171004.66</v>
+        <v>186130.23</v>
       </c>
       <c r="J362" t="n">
         <v>23</v>
@@ -14939,10 +14939,10 @@
         <v>0</v>
       </c>
       <c r="H363" t="n">
-        <v>232294.8</v>
+        <v>213818.7</v>
       </c>
       <c r="I363" t="n">
-        <v>195382.32</v>
+        <v>179239.01</v>
       </c>
       <c r="J363" t="n">
         <v>14</v>
@@ -14979,10 +14979,10 @@
         <v>0</v>
       </c>
       <c r="H364" t="n">
-        <v>220063</v>
+        <v>229545.86</v>
       </c>
       <c r="I364" t="n">
-        <v>185937.63</v>
+        <v>193592.75</v>
       </c>
       <c r="J364" t="n">
         <v>9</v>
@@ -15019,10 +15019,10 @@
         <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>97773.23</v>
+        <v>103506.08</v>
       </c>
       <c r="I365" t="n">
-        <v>97286.21000000001</v>
+        <v>86964.13</v>
       </c>
       <c r="J365" t="n">
         <v>11</v>
@@ -15059,10 +15059,10 @@
         <v>0</v>
       </c>
       <c r="H366" t="n">
-        <v>94469.8</v>
+        <v>100719.7</v>
       </c>
       <c r="I366" t="n">
-        <v>94738.23</v>
+        <v>101433.47</v>
       </c>
       <c r="J366" t="n">
         <v>6</v>
@@ -15099,10 +15099,10 @@
         <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>85880.69</v>
+        <v>100272.76</v>
       </c>
       <c r="I367" t="n">
-        <v>86815.88</v>
+        <v>101563.08</v>
       </c>
       <c r="J367" t="n">
         <v>4</v>
@@ -15136,13 +15136,13 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>272189.48</v>
+        <v>261513.29</v>
       </c>
       <c r="H368" t="n">
-        <v>66584.34</v>
+        <v>71585.82000000001</v>
       </c>
       <c r="I368" t="n">
-        <v>65797.67999999999</v>
+        <v>70568.60000000001</v>
       </c>
       <c r="J368" t="n">
         <v>20</v>
@@ -15176,13 +15176,13 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>159305.11</v>
+        <v>158098.49</v>
       </c>
       <c r="H369" t="n">
-        <v>76442.33</v>
+        <v>68884.17999999999</v>
       </c>
       <c r="I369" t="n">
-        <v>75803.03</v>
+        <v>69591.21000000001</v>
       </c>
       <c r="J369" t="n">
         <v>12</v>
@@ -15216,13 +15216,13 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>103772.89</v>
+        <v>105890.23</v>
       </c>
       <c r="H370" t="n">
-        <v>72469.73</v>
+        <v>76952.22</v>
       </c>
       <c r="I370" t="n">
-        <v>70915.97</v>
+        <v>77427.21000000001</v>
       </c>
       <c r="J370" t="n">
         <v>8</v>
@@ -15259,10 +15259,10 @@
         <v>0</v>
       </c>
       <c r="H371" t="n">
-        <v>54311.01</v>
+        <v>58050.67</v>
       </c>
       <c r="I371" t="n">
-        <v>53767.85</v>
+        <v>57790.39</v>
       </c>
       <c r="J371" t="n">
         <v>7</v>
@@ -15299,10 +15299,10 @@
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>55629.84</v>
+        <v>51575.84</v>
       </c>
       <c r="I372" t="n">
-        <v>55704.9</v>
+        <v>51490.34</v>
       </c>
       <c r="J372" t="n">
         <v>4</v>
@@ -15339,10 +15339,10 @@
         <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>52734.97</v>
+        <v>52331.11</v>
       </c>
       <c r="I373" t="n">
-        <v>51425.61</v>
+        <v>52899.41</v>
       </c>
       <c r="J373" t="n">
         <v>3</v>
@@ -15379,10 +15379,10 @@
         <v>0</v>
       </c>
       <c r="H374" t="n">
-        <v>75934.31</v>
+        <v>85917.21000000001</v>
       </c>
       <c r="I374" t="n">
-        <v>74477.09</v>
+        <v>85101.08</v>
       </c>
       <c r="J374" t="n">
         <v>15</v>
@@ -15419,10 +15419,10 @@
         <v>0</v>
       </c>
       <c r="H375" t="n">
-        <v>93300.07000000001</v>
+        <v>85585.75999999999</v>
       </c>
       <c r="I375" t="n">
-        <v>93829.94</v>
+        <v>85415.31</v>
       </c>
       <c r="J375" t="n">
         <v>9</v>
@@ -15459,10 +15459,10 @@
         <v>0</v>
       </c>
       <c r="H376" t="n">
-        <v>85151.28999999999</v>
+        <v>83185.35000000001</v>
       </c>
       <c r="I376" t="n">
-        <v>83533.61</v>
+        <v>83519.06</v>
       </c>
       <c r="J376" t="n">
         <v>6</v>
@@ -15499,10 +15499,10 @@
         <v>0</v>
       </c>
       <c r="H377" t="n">
-        <v>182335.16</v>
+        <v>193642.66</v>
       </c>
       <c r="I377" t="n">
-        <v>153578.01</v>
+        <v>162497.74</v>
       </c>
       <c r="J377" t="n">
         <v>23</v>
@@ -15539,10 +15539,10 @@
         <v>0</v>
       </c>
       <c r="H378" t="n">
-        <v>205535.8</v>
+        <v>221394.26</v>
       </c>
       <c r="I378" t="n">
-        <v>171668.94</v>
+        <v>185766.32</v>
       </c>
       <c r="J378" t="n">
         <v>14</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="H379" t="n">
-        <v>211406.47</v>
+        <v>195075.04</v>
       </c>
       <c r="I379" t="n">
-        <v>177503.41</v>
+        <v>165969.06</v>
       </c>
       <c r="J379" t="n">
         <v>9</v>
@@ -15619,10 +15619,10 @@
         <v>0</v>
       </c>
       <c r="H380" t="n">
-        <v>103412.52</v>
+        <v>97022.25</v>
       </c>
       <c r="I380" t="n">
-        <v>102527.92</v>
+        <v>97353.45</v>
       </c>
       <c r="J380" t="n">
         <v>11</v>
@@ -15659,10 +15659,10 @@
         <v>0</v>
       </c>
       <c r="H381" t="n">
-        <v>95131.92</v>
+        <v>97359.75</v>
       </c>
       <c r="I381" t="n">
-        <v>96386.05</v>
+        <v>94303.89999999999</v>
       </c>
       <c r="J381" t="n">
         <v>6</v>
@@ -15699,10 +15699,10 @@
         <v>0</v>
       </c>
       <c r="H382" t="n">
-        <v>116101.09</v>
+        <v>104564.19</v>
       </c>
       <c r="I382" t="n">
-        <v>94972.00999999999</v>
+        <v>92188.78</v>
       </c>
       <c r="J382" t="n">
         <v>4</v>
@@ -15736,13 +15736,13 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>262775.48</v>
+        <v>280743.25</v>
       </c>
       <c r="H383" t="n">
-        <v>69499.69</v>
+        <v>61698.29</v>
       </c>
       <c r="I383" t="n">
-        <v>69061.92</v>
+        <v>60548.92</v>
       </c>
       <c r="J383" t="n">
         <v>20</v>
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>157017.56</v>
+        <v>153394.96</v>
       </c>
       <c r="H384" t="n">
-        <v>77132.88</v>
+        <v>78296.56</v>
       </c>
       <c r="I384" t="n">
-        <v>77729.63</v>
+        <v>77042.91</v>
       </c>
       <c r="J384" t="n">
         <v>12</v>
@@ -15816,13 +15816,13 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>110386.42</v>
+        <v>107145.34</v>
       </c>
       <c r="H385" t="n">
-        <v>77881.73</v>
+        <v>75812.56</v>
       </c>
       <c r="I385" t="n">
-        <v>77380.31</v>
+        <v>76281.24000000001</v>
       </c>
       <c r="J385" t="n">
         <v>8</v>
@@ -15859,10 +15859,10 @@
         <v>0</v>
       </c>
       <c r="H386" t="n">
-        <v>56324.12</v>
+        <v>57050.7</v>
       </c>
       <c r="I386" t="n">
-        <v>55575.12</v>
+        <v>56862.21</v>
       </c>
       <c r="J386" t="n">
         <v>7</v>
@@ -15899,10 +15899,10 @@
         <v>0</v>
       </c>
       <c r="H387" t="n">
-        <v>52145.61</v>
+        <v>52029.29</v>
       </c>
       <c r="I387" t="n">
-        <v>52810.38</v>
+        <v>52294.09</v>
       </c>
       <c r="J387" t="n">
         <v>4</v>
@@ -15939,10 +15939,10 @@
         <v>0</v>
       </c>
       <c r="H388" t="n">
-        <v>55804.22</v>
+        <v>55548.28</v>
       </c>
       <c r="I388" t="n">
-        <v>55884.54</v>
+        <v>54630.44</v>
       </c>
       <c r="J388" t="n">
         <v>3</v>
@@ -15979,10 +15979,10 @@
         <v>0</v>
       </c>
       <c r="H389" t="n">
-        <v>82157.61</v>
+        <v>84119.96000000001</v>
       </c>
       <c r="I389" t="n">
-        <v>81733.07000000001</v>
+        <v>83319.03999999999</v>
       </c>
       <c r="J389" t="n">
         <v>15</v>
@@ -16019,10 +16019,10 @@
         <v>0</v>
       </c>
       <c r="H390" t="n">
-        <v>83603.89</v>
+        <v>90224.56</v>
       </c>
       <c r="I390" t="n">
-        <v>82450.16</v>
+        <v>90441.13</v>
       </c>
       <c r="J390" t="n">
         <v>9</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="H391" t="n">
-        <v>74252.57000000001</v>
+        <v>81006.07000000001</v>
       </c>
       <c r="I391" t="n">
-        <v>72774.98</v>
+        <v>80582.78</v>
       </c>
       <c r="J391" t="n">
         <v>6</v>
@@ -16099,10 +16099,10 @@
         <v>0</v>
       </c>
       <c r="H392" t="n">
-        <v>222663.3</v>
+        <v>199576.6</v>
       </c>
       <c r="I392" t="n">
-        <v>188586.32</v>
+        <v>168545.31</v>
       </c>
       <c r="J392" t="n">
         <v>23</v>
@@ -16139,10 +16139,10 @@
         <v>0</v>
       </c>
       <c r="H393" t="n">
-        <v>213599.35</v>
+        <v>211003.48</v>
       </c>
       <c r="I393" t="n">
-        <v>181487.36</v>
+        <v>179425.82</v>
       </c>
       <c r="J393" t="n">
         <v>14</v>
@@ -16179,10 +16179,10 @@
         <v>0</v>
       </c>
       <c r="H394" t="n">
-        <v>192226.01</v>
+        <v>210263.64</v>
       </c>
       <c r="I394" t="n">
-        <v>161761.86</v>
+        <v>177198.73</v>
       </c>
       <c r="J394" t="n">
         <v>9</v>
@@ -16219,10 +16219,10 @@
         <v>0</v>
       </c>
       <c r="H395" t="n">
-        <v>106192.8</v>
+        <v>94946.92999999999</v>
       </c>
       <c r="I395" t="n">
-        <v>92737.42999999999</v>
+        <v>93881.61</v>
       </c>
       <c r="J395" t="n">
         <v>11</v>
@@ -16259,10 +16259,10 @@
         <v>0</v>
       </c>
       <c r="H396" t="n">
-        <v>124383.1</v>
+        <v>122293.55</v>
       </c>
       <c r="I396" t="n">
-        <v>105709.64</v>
+        <v>95406.33</v>
       </c>
       <c r="J396" t="n">
         <v>6</v>
@@ -16299,10 +16299,10 @@
         <v>0</v>
       </c>
       <c r="H397" t="n">
-        <v>96762.87</v>
+        <v>102920.9</v>
       </c>
       <c r="I397" t="n">
-        <v>97141.39</v>
+        <v>102169.64</v>
       </c>
       <c r="J397" t="n">
         <v>4</v>
@@ -16336,13 +16336,13 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>300026.54</v>
+        <v>290818.75</v>
       </c>
       <c r="H398" t="n">
-        <v>78026.37</v>
+        <v>73611.35000000001</v>
       </c>
       <c r="I398" t="n">
-        <v>79410.17999999999</v>
+        <v>76119.92</v>
       </c>
       <c r="J398" t="n">
         <v>20</v>
@@ -16376,13 +16376,13 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>175466.59</v>
+        <v>185837.63</v>
       </c>
       <c r="H399" t="n">
-        <v>72447.48</v>
+        <v>81361.7</v>
       </c>
       <c r="I399" t="n">
-        <v>74483.97</v>
+        <v>79954</v>
       </c>
       <c r="J399" t="n">
         <v>12</v>
@@ -16416,13 +16416,13 @@
         </is>
       </c>
       <c r="G400" t="n">
-        <v>117420.42</v>
+        <v>108715.09</v>
       </c>
       <c r="H400" t="n">
-        <v>77307.14</v>
+        <v>64580.55</v>
       </c>
       <c r="I400" t="n">
-        <v>78449.86</v>
+        <v>64143.6</v>
       </c>
       <c r="J400" t="n">
         <v>8</v>
@@ -16459,10 +16459,10 @@
         <v>0</v>
       </c>
       <c r="H401" t="n">
-        <v>52620.59</v>
+        <v>51935.1</v>
       </c>
       <c r="I401" t="n">
-        <v>54501.28</v>
+        <v>51821.8</v>
       </c>
       <c r="J401" t="n">
         <v>7</v>
@@ -16499,10 +16499,10 @@
         <v>0</v>
       </c>
       <c r="H402" t="n">
-        <v>55267.94</v>
+        <v>50853.09</v>
       </c>
       <c r="I402" t="n">
-        <v>55026.65</v>
+        <v>51745.64</v>
       </c>
       <c r="J402" t="n">
         <v>4</v>
@@ -16539,10 +16539,10 @@
         <v>0</v>
       </c>
       <c r="H403" t="n">
-        <v>53111.63</v>
+        <v>56884.17</v>
       </c>
       <c r="I403" t="n">
-        <v>54101.09</v>
+        <v>56119.13</v>
       </c>
       <c r="J403" t="n">
         <v>3</v>
@@ -16579,10 +16579,10 @@
         <v>0</v>
       </c>
       <c r="H404" t="n">
-        <v>81047.64</v>
+        <v>89953.99000000001</v>
       </c>
       <c r="I404" t="n">
-        <v>81556.41</v>
+        <v>90467.69</v>
       </c>
       <c r="J404" t="n">
         <v>15</v>
@@ -16619,10 +16619,10 @@
         <v>0</v>
       </c>
       <c r="H405" t="n">
-        <v>86772.89999999999</v>
+        <v>94883.74000000001</v>
       </c>
       <c r="I405" t="n">
-        <v>86058.44</v>
+        <v>93808.53999999999</v>
       </c>
       <c r="J405" t="n">
         <v>9</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="H406" t="n">
-        <v>81653.34</v>
+        <v>78183.7</v>
       </c>
       <c r="I406" t="n">
-        <v>80590.44</v>
+        <v>77913.94</v>
       </c>
       <c r="J406" t="n">
         <v>6</v>
@@ -16699,10 +16699,10 @@
         <v>0</v>
       </c>
       <c r="H407" t="n">
-        <v>247092.98</v>
+        <v>221108.06</v>
       </c>
       <c r="I407" t="n">
-        <v>208178.76</v>
+        <v>185707.46</v>
       </c>
       <c r="J407" t="n">
         <v>23</v>
@@ -16739,10 +16739,10 @@
         <v>0</v>
       </c>
       <c r="H408" t="n">
-        <v>184494.16</v>
+        <v>215548.73</v>
       </c>
       <c r="I408" t="n">
-        <v>157106.49</v>
+        <v>182472.51</v>
       </c>
       <c r="J408" t="n">
         <v>14</v>
@@ -16779,10 +16779,10 @@
         <v>0</v>
       </c>
       <c r="H409" t="n">
-        <v>207832.97</v>
+        <v>255865.35</v>
       </c>
       <c r="I409" t="n">
-        <v>175853.62</v>
+        <v>216497.16</v>
       </c>
       <c r="J409" t="n">
         <v>9</v>
@@ -16819,10 +16819,10 @@
         <v>0</v>
       </c>
       <c r="H410" t="n">
-        <v>104262.68</v>
+        <v>122300.83</v>
       </c>
       <c r="I410" t="n">
-        <v>106042.96</v>
+        <v>98176.31</v>
       </c>
       <c r="J410" t="n">
         <v>11</v>
@@ -16859,10 +16859,10 @@
         <v>0</v>
       </c>
       <c r="H411" t="n">
-        <v>117289.59</v>
+        <v>102336.81</v>
       </c>
       <c r="I411" t="n">
-        <v>103603.17</v>
+        <v>103457.91</v>
       </c>
       <c r="J411" t="n">
         <v>6</v>
@@ -16899,10 +16899,10 @@
         <v>0</v>
       </c>
       <c r="H412" t="n">
-        <v>93828.67</v>
+        <v>97212.89999999999</v>
       </c>
       <c r="I412" t="n">
-        <v>95075.82000000001</v>
+        <v>97410.42</v>
       </c>
       <c r="J412" t="n">
         <v>4</v>
@@ -16936,13 +16936,13 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>298935.7</v>
+        <v>300513.95</v>
       </c>
       <c r="H413" t="n">
-        <v>76853.60000000001</v>
+        <v>78401.34</v>
       </c>
       <c r="I413" t="n">
-        <v>76998.07000000001</v>
+        <v>78505.63</v>
       </c>
       <c r="J413" t="n">
         <v>20</v>
@@ -16976,13 +16976,13 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>191914.86</v>
+        <v>177960.2</v>
       </c>
       <c r="H414" t="n">
-        <v>75782.3</v>
+        <v>76968.13</v>
       </c>
       <c r="I414" t="n">
-        <v>76798.97</v>
+        <v>77505.7</v>
       </c>
       <c r="J414" t="n">
         <v>12</v>
@@ -17016,13 +17016,13 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>111780.78</v>
+        <v>113685.31</v>
       </c>
       <c r="H415" t="n">
-        <v>74443.64</v>
+        <v>72304.16</v>
       </c>
       <c r="I415" t="n">
-        <v>75001.22</v>
+        <v>71438.75</v>
       </c>
       <c r="J415" t="n">
         <v>8</v>
@@ -17059,10 +17059,10 @@
         <v>0</v>
       </c>
       <c r="H416" t="n">
-        <v>59069.3</v>
+        <v>55679.41</v>
       </c>
       <c r="I416" t="n">
-        <v>59582.47</v>
+        <v>56165.16</v>
       </c>
       <c r="J416" t="n">
         <v>7</v>
@@ -17099,10 +17099,10 @@
         <v>0</v>
       </c>
       <c r="H417" t="n">
-        <v>52798.77</v>
+        <v>51153.69</v>
       </c>
       <c r="I417" t="n">
-        <v>52894.65</v>
+        <v>51468.83</v>
       </c>
       <c r="J417" t="n">
         <v>4</v>
@@ -17139,10 +17139,10 @@
         <v>0</v>
       </c>
       <c r="H418" t="n">
-        <v>56072.03</v>
+        <v>51420.62</v>
       </c>
       <c r="I418" t="n">
-        <v>56037.37</v>
+        <v>52212.64</v>
       </c>
       <c r="J418" t="n">
         <v>3</v>
@@ -17179,10 +17179,10 @@
         <v>0</v>
       </c>
       <c r="H419" t="n">
-        <v>88529.67</v>
+        <v>82702.78999999999</v>
       </c>
       <c r="I419" t="n">
-        <v>87166.98</v>
+        <v>82831.5</v>
       </c>
       <c r="J419" t="n">
         <v>15</v>
@@ -17219,10 +17219,10 @@
         <v>0</v>
       </c>
       <c r="H420" t="n">
-        <v>82322.41</v>
+        <v>82436.03</v>
       </c>
       <c r="I420" t="n">
-        <v>82143.25</v>
+        <v>83847.49000000001</v>
       </c>
       <c r="J420" t="n">
         <v>9</v>
@@ -17259,10 +17259,10 @@
         <v>0</v>
       </c>
       <c r="H421" t="n">
-        <v>77947.64999999999</v>
+        <v>81863.98</v>
       </c>
       <c r="I421" t="n">
-        <v>76132.09</v>
+        <v>83642.86</v>
       </c>
       <c r="J421" t="n">
         <v>6</v>
@@ -17299,10 +17299,10 @@
         <v>0</v>
       </c>
       <c r="H422" t="n">
-        <v>236953.11</v>
+        <v>208726.6</v>
       </c>
       <c r="I422" t="n">
-        <v>199455.62</v>
+        <v>175705.85</v>
       </c>
       <c r="J422" t="n">
         <v>23</v>
@@ -17339,10 +17339,10 @@
         <v>0</v>
       </c>
       <c r="H423" t="n">
-        <v>235010.56</v>
+        <v>193860.11</v>
       </c>
       <c r="I423" t="n">
-        <v>199080.45</v>
+        <v>164040.1</v>
       </c>
       <c r="J423" t="n">
         <v>14</v>
@@ -17379,10 +17379,10 @@
         <v>0</v>
       </c>
       <c r="H424" t="n">
-        <v>219736.07</v>
+        <v>199270.7</v>
       </c>
       <c r="I424" t="n">
-        <v>184589.03</v>
+        <v>168844.72</v>
       </c>
       <c r="J424" t="n">
         <v>9</v>
@@ -17419,10 +17419,10 @@
         <v>0</v>
       </c>
       <c r="H425" t="n">
-        <v>102537.7</v>
+        <v>93225.86</v>
       </c>
       <c r="I425" t="n">
-        <v>104050.92</v>
+        <v>93740.27</v>
       </c>
       <c r="J425" t="n">
         <v>11</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="H426" t="n">
-        <v>89579.25</v>
+        <v>91465.71000000001</v>
       </c>
       <c r="I426" t="n">
-        <v>91313.3</v>
+        <v>90619</v>
       </c>
       <c r="J426" t="n">
         <v>6</v>
@@ -17499,10 +17499,10 @@
         <v>0</v>
       </c>
       <c r="H427" t="n">
-        <v>85606.45</v>
+        <v>120149.1</v>
       </c>
       <c r="I427" t="n">
-        <v>85205.81</v>
+        <v>98149.66</v>
       </c>
       <c r="J427" t="n">
         <v>4</v>
@@ -17536,13 +17536,13 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>311950.15</v>
+        <v>302062.59</v>
       </c>
       <c r="H428" t="n">
-        <v>86538.39999999999</v>
+        <v>76681.62</v>
       </c>
       <c r="I428" t="n">
-        <v>85220.41</v>
+        <v>74345.83</v>
       </c>
       <c r="J428" t="n">
         <v>20</v>
@@ -17576,13 +17576,13 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>164506.64</v>
+        <v>169516.26</v>
       </c>
       <c r="H429" t="n">
-        <v>77076.64999999999</v>
+        <v>75560.25</v>
       </c>
       <c r="I429" t="n">
-        <v>76400.42999999999</v>
+        <v>74880.77</v>
       </c>
       <c r="J429" t="n">
         <v>12</v>
@@ -17616,13 +17616,13 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>120446.41</v>
+        <v>122197.04</v>
       </c>
       <c r="H430" t="n">
-        <v>88347.25999999999</v>
+        <v>69644.05</v>
       </c>
       <c r="I430" t="n">
-        <v>88550.14999999999</v>
+        <v>68101.13</v>
       </c>
       <c r="J430" t="n">
         <v>8</v>
@@ -17659,10 +17659,10 @@
         <v>0</v>
       </c>
       <c r="H431" t="n">
-        <v>58254.01</v>
+        <v>55848.44</v>
       </c>
       <c r="I431" t="n">
-        <v>57783.77</v>
+        <v>57085.62</v>
       </c>
       <c r="J431" t="n">
         <v>7</v>
@@ -17699,10 +17699,10 @@
         <v>0</v>
       </c>
       <c r="H432" t="n">
-        <v>57051.46</v>
+        <v>55959.54</v>
       </c>
       <c r="I432" t="n">
-        <v>57817.68</v>
+        <v>56589.45</v>
       </c>
       <c r="J432" t="n">
         <v>4</v>
@@ -17739,10 +17739,10 @@
         <v>0</v>
       </c>
       <c r="H433" t="n">
-        <v>54230.55</v>
+        <v>50627.32</v>
       </c>
       <c r="I433" t="n">
-        <v>52490.61</v>
+        <v>50359.84</v>
       </c>
       <c r="J433" t="n">
         <v>3</v>
@@ -17779,10 +17779,10 @@
         <v>0</v>
       </c>
       <c r="H434" t="n">
-        <v>91672.91</v>
+        <v>79308.46000000001</v>
       </c>
       <c r="I434" t="n">
-        <v>92592.60000000001</v>
+        <v>80415.50999999999</v>
       </c>
       <c r="J434" t="n">
         <v>15</v>
@@ -17819,10 +17819,10 @@
         <v>0</v>
       </c>
       <c r="H435" t="n">
-        <v>84391.58</v>
+        <v>74379.11</v>
       </c>
       <c r="I435" t="n">
-        <v>86437.69</v>
+        <v>74658.17999999999</v>
       </c>
       <c r="J435" t="n">
         <v>9</v>
@@ -17859,10 +17859,10 @@
         <v>0</v>
       </c>
       <c r="H436" t="n">
-        <v>85554.85000000001</v>
+        <v>87116.09</v>
       </c>
       <c r="I436" t="n">
-        <v>84809.57000000001</v>
+        <v>86042.28</v>
       </c>
       <c r="J436" t="n">
         <v>6</v>
@@ -17899,10 +17899,10 @@
         <v>0</v>
       </c>
       <c r="H437" t="n">
-        <v>206612.04</v>
+        <v>208879.49</v>
       </c>
       <c r="I437" t="n">
-        <v>174791.24</v>
+        <v>175741.98</v>
       </c>
       <c r="J437" t="n">
         <v>23</v>
@@ -17939,10 +17939,10 @@
         <v>0</v>
       </c>
       <c r="H438" t="n">
-        <v>213815.5</v>
+        <v>208508.64</v>
       </c>
       <c r="I438" t="n">
-        <v>179876.15</v>
+        <v>175661.61</v>
       </c>
       <c r="J438" t="n">
         <v>14</v>
@@ -17979,10 +17979,10 @@
         <v>0</v>
       </c>
       <c r="H439" t="n">
-        <v>209025.3</v>
+        <v>231898.11</v>
       </c>
       <c r="I439" t="n">
-        <v>176907.66</v>
+        <v>196852.47</v>
       </c>
       <c r="J439" t="n">
         <v>9</v>
@@ -18019,10 +18019,10 @@
         <v>0</v>
       </c>
       <c r="H440" t="n">
-        <v>111628.03</v>
+        <v>119016.71</v>
       </c>
       <c r="I440" t="n">
-        <v>92704.19</v>
+        <v>98014.89</v>
       </c>
       <c r="J440" t="n">
         <v>11</v>
@@ -18059,10 +18059,10 @@
         <v>0</v>
       </c>
       <c r="H441" t="n">
-        <v>117671.4</v>
+        <v>111881.82</v>
       </c>
       <c r="I441" t="n">
-        <v>98374.44</v>
+        <v>113396.62</v>
       </c>
       <c r="J441" t="n">
         <v>6</v>
@@ -18099,10 +18099,10 @@
         <v>0</v>
       </c>
       <c r="H442" t="n">
-        <v>90991.07000000001</v>
+        <v>103114.02</v>
       </c>
       <c r="I442" t="n">
-        <v>91581.5</v>
+        <v>103888.4</v>
       </c>
       <c r="J442" t="n">
         <v>4</v>
@@ -18136,13 +18136,13 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>305144.35</v>
+        <v>295193.13</v>
       </c>
       <c r="H443" t="n">
-        <v>74188.66</v>
+        <v>68619.92</v>
       </c>
       <c r="I443" t="n">
-        <v>73023.8</v>
+        <v>67813.71000000001</v>
       </c>
       <c r="J443" t="n">
         <v>20</v>
@@ -18176,13 +18176,13 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>174529.02</v>
+        <v>181067.86</v>
       </c>
       <c r="H444" t="n">
-        <v>76483.39999999999</v>
+        <v>77715.82000000001</v>
       </c>
       <c r="I444" t="n">
-        <v>77863.64999999999</v>
+        <v>77391.06</v>
       </c>
       <c r="J444" t="n">
         <v>12</v>
@@ -18216,13 +18216,13 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>131817.47</v>
+        <v>118913.82</v>
       </c>
       <c r="H445" t="n">
-        <v>70165.45</v>
+        <v>83390.03</v>
       </c>
       <c r="I445" t="n">
-        <v>69716.50999999999</v>
+        <v>85162.71000000001</v>
       </c>
       <c r="J445" t="n">
         <v>8</v>
@@ -18259,10 +18259,10 @@
         <v>0</v>
       </c>
       <c r="H446" t="n">
-        <v>56790.27</v>
+        <v>52311.9</v>
       </c>
       <c r="I446" t="n">
-        <v>57237.46</v>
+        <v>52097.97</v>
       </c>
       <c r="J446" t="n">
         <v>7</v>
@@ -18299,10 +18299,10 @@
         <v>0</v>
       </c>
       <c r="H447" t="n">
-        <v>58968.43</v>
+        <v>51341.2</v>
       </c>
       <c r="I447" t="n">
-        <v>58767.03</v>
+        <v>51581.91</v>
       </c>
       <c r="J447" t="n">
         <v>4</v>
@@ -18339,10 +18339,10 @@
         <v>0</v>
       </c>
       <c r="H448" t="n">
-        <v>49631.94</v>
+        <v>58780.5</v>
       </c>
       <c r="I448" t="n">
-        <v>49049.13</v>
+        <v>60422.78</v>
       </c>
       <c r="J448" t="n">
         <v>3</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="H449" t="n">
-        <v>81611.05</v>
+        <v>87106.60000000001</v>
       </c>
       <c r="I449" t="n">
-        <v>82940.34</v>
+        <v>88429.16</v>
       </c>
       <c r="J449" t="n">
         <v>15</v>
@@ -18419,10 +18419,10 @@
         <v>0</v>
       </c>
       <c r="H450" t="n">
-        <v>94818.17999999999</v>
+        <v>90855.3</v>
       </c>
       <c r="I450" t="n">
-        <v>94531.37</v>
+        <v>90014.02</v>
       </c>
       <c r="J450" t="n">
         <v>9</v>
@@ -18459,10 +18459,10 @@
         <v>0</v>
       </c>
       <c r="H451" t="n">
-        <v>86563.39</v>
+        <v>89300.07000000001</v>
       </c>
       <c r="I451" t="n">
-        <v>87200.88</v>
+        <v>89975.99000000001</v>
       </c>
       <c r="J451" t="n">
         <v>6</v>
@@ -18499,10 +18499,10 @@
         <v>0</v>
       </c>
       <c r="H452" t="n">
-        <v>195312.49</v>
+        <v>221343.57</v>
       </c>
       <c r="I452" t="n">
-        <v>164831.89</v>
+        <v>188438.42</v>
       </c>
       <c r="J452" t="n">
         <v>23</v>
@@ -18539,10 +18539,10 @@
         <v>0</v>
       </c>
       <c r="H453" t="n">
-        <v>211725.87</v>
+        <v>219466.51</v>
       </c>
       <c r="I453" t="n">
-        <v>179008.38</v>
+        <v>184735.7</v>
       </c>
       <c r="J453" t="n">
         <v>14</v>
@@ -18579,10 +18579,10 @@
         <v>0</v>
       </c>
       <c r="H454" t="n">
-        <v>204644.71</v>
+        <v>219920</v>
       </c>
       <c r="I454" t="n">
-        <v>171426.87</v>
+        <v>185610.89</v>
       </c>
       <c r="J454" t="n">
         <v>9</v>
@@ -18619,10 +18619,10 @@
         <v>0</v>
       </c>
       <c r="H455" t="n">
-        <v>97578.92</v>
+        <v>91332.14999999999</v>
       </c>
       <c r="I455" t="n">
-        <v>97940.73</v>
+        <v>91571.7</v>
       </c>
       <c r="J455" t="n">
         <v>11</v>
@@ -18659,10 +18659,10 @@
         <v>0</v>
       </c>
       <c r="H456" t="n">
-        <v>95524.47</v>
+        <v>95375.73</v>
       </c>
       <c r="I456" t="n">
-        <v>98506.78999999999</v>
+        <v>92844.52</v>
       </c>
       <c r="J456" t="n">
         <v>6</v>
@@ -18699,10 +18699,10 @@
         <v>0</v>
       </c>
       <c r="H457" t="n">
-        <v>119348.14</v>
+        <v>108139.61</v>
       </c>
       <c r="I457" t="n">
-        <v>95094.75</v>
+        <v>91478.84</v>
       </c>
       <c r="J457" t="n">
         <v>4</v>
@@ -18736,13 +18736,13 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>283777.58</v>
+        <v>280554.69</v>
       </c>
       <c r="H458" t="n">
-        <v>66771.23</v>
+        <v>71138.81</v>
       </c>
       <c r="I458" t="n">
-        <v>66218.28</v>
+        <v>70173.00999999999</v>
       </c>
       <c r="J458" t="n">
         <v>20</v>
@@ -18776,13 +18776,13 @@
         </is>
       </c>
       <c r="G459" t="n">
-        <v>178374.14</v>
+        <v>174748.13</v>
       </c>
       <c r="H459" t="n">
-        <v>64352.17</v>
+        <v>74611.86</v>
       </c>
       <c r="I459" t="n">
-        <v>65157.37</v>
+        <v>76182.09</v>
       </c>
       <c r="J459" t="n">
         <v>12</v>
@@ -18816,13 +18816,13 @@
         </is>
       </c>
       <c r="G460" t="n">
-        <v>119529.88</v>
+        <v>114711.41</v>
       </c>
       <c r="H460" t="n">
-        <v>74798.09</v>
+        <v>76666.14</v>
       </c>
       <c r="I460" t="n">
-        <v>75357.48</v>
+        <v>76507.49000000001</v>
       </c>
       <c r="J460" t="n">
         <v>8</v>
@@ -18859,10 +18859,10 @@
         <v>0</v>
       </c>
       <c r="H461" t="n">
-        <v>56968.66</v>
+        <v>50897.18</v>
       </c>
       <c r="I461" t="n">
-        <v>56214.63</v>
+        <v>50160.33</v>
       </c>
       <c r="J461" t="n">
         <v>7</v>
@@ -18899,10 +18899,10 @@
         <v>0</v>
       </c>
       <c r="H462" t="n">
-        <v>56026.34</v>
+        <v>53914.65</v>
       </c>
       <c r="I462" t="n">
-        <v>56597.69</v>
+        <v>54749.74</v>
       </c>
       <c r="J462" t="n">
         <v>4</v>
@@ -18939,10 +18939,10 @@
         <v>0</v>
       </c>
       <c r="H463" t="n">
-        <v>59929.68</v>
+        <v>55204.2</v>
       </c>
       <c r="I463" t="n">
-        <v>60724.99</v>
+        <v>55727.29</v>
       </c>
       <c r="J463" t="n">
         <v>3</v>
@@ -18979,10 +18979,10 @@
         <v>0</v>
       </c>
       <c r="H464" t="n">
-        <v>76571.56</v>
+        <v>70963.66</v>
       </c>
       <c r="I464" t="n">
-        <v>78617.39999999999</v>
+        <v>70301.36</v>
       </c>
       <c r="J464" t="n">
         <v>15</v>
@@ -19019,10 +19019,10 @@
         <v>0</v>
       </c>
       <c r="H465" t="n">
-        <v>83790.22</v>
+        <v>85401.47</v>
       </c>
       <c r="I465" t="n">
-        <v>84504.64</v>
+        <v>86606.2</v>
       </c>
       <c r="J465" t="n">
         <v>9</v>
@@ -19059,10 +19059,10 @@
         <v>0</v>
       </c>
       <c r="H466" t="n">
-        <v>80554.8</v>
+        <v>88120.00999999999</v>
       </c>
       <c r="I466" t="n">
-        <v>81363.13</v>
+        <v>88490.10000000001</v>
       </c>
       <c r="J466" t="n">
         <v>6</v>
@@ -19099,10 +19099,10 @@
         <v>0</v>
       </c>
       <c r="H467" t="n">
-        <v>233296.59</v>
+        <v>224323.76</v>
       </c>
       <c r="I467" t="n">
-        <v>196554.93</v>
+        <v>190148.92</v>
       </c>
       <c r="J467" t="n">
         <v>23</v>
@@ -19139,10 +19139,10 @@
         <v>0</v>
       </c>
       <c r="H468" t="n">
-        <v>200647.13</v>
+        <v>232715.16</v>
       </c>
       <c r="I468" t="n">
-        <v>168615.91</v>
+        <v>196832.59</v>
       </c>
       <c r="J468" t="n">
         <v>14</v>
@@ -19179,10 +19179,10 @@
         <v>0</v>
       </c>
       <c r="H469" t="n">
-        <v>224857.57</v>
+        <v>200072.29</v>
       </c>
       <c r="I469" t="n">
-        <v>191177.34</v>
+        <v>168378.27</v>
       </c>
       <c r="J469" t="n">
         <v>9</v>
@@ -19219,10 +19219,10 @@
         <v>0</v>
       </c>
       <c r="H470" t="n">
-        <v>103266.22</v>
+        <v>112494.64</v>
       </c>
       <c r="I470" t="n">
-        <v>103643.44</v>
+        <v>98675.62</v>
       </c>
       <c r="J470" t="n">
         <v>11</v>
@@ -19259,10 +19259,10 @@
         <v>0</v>
       </c>
       <c r="H471" t="n">
-        <v>94664.19</v>
+        <v>93665.88</v>
       </c>
       <c r="I471" t="n">
-        <v>93824.53999999999</v>
+        <v>95129.55</v>
       </c>
       <c r="J471" t="n">
         <v>6</v>
@@ -19299,10 +19299,10 @@
         <v>0</v>
       </c>
       <c r="H472" t="n">
-        <v>93451.58</v>
+        <v>108308.99</v>
       </c>
       <c r="I472" t="n">
-        <v>90791.50999999999</v>
+        <v>107334.68</v>
       </c>
       <c r="J472" t="n">
         <v>4</v>
@@ -19336,13 +19336,13 @@
         </is>
       </c>
       <c r="G473" t="n">
-        <v>290926.61</v>
+        <v>302631.45</v>
       </c>
       <c r="H473" t="n">
-        <v>71313.58</v>
+        <v>79323.49000000001</v>
       </c>
       <c r="I473" t="n">
-        <v>71662</v>
+        <v>81419.03</v>
       </c>
       <c r="J473" t="n">
         <v>20</v>
@@ -19376,13 +19376,13 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>191026.39</v>
+        <v>187424.21</v>
       </c>
       <c r="H474" t="n">
-        <v>70949.46000000001</v>
+        <v>79725.95</v>
       </c>
       <c r="I474" t="n">
-        <v>69765.62</v>
+        <v>78241.64</v>
       </c>
       <c r="J474" t="n">
         <v>12</v>
@@ -19416,13 +19416,13 @@
         </is>
       </c>
       <c r="G475" t="n">
-        <v>115349.38</v>
+        <v>112384.46</v>
       </c>
       <c r="H475" t="n">
-        <v>73449.56</v>
+        <v>73356.78999999999</v>
       </c>
       <c r="I475" t="n">
-        <v>73080.73</v>
+        <v>72947.91</v>
       </c>
       <c r="J475" t="n">
         <v>8</v>
@@ -19459,10 +19459,10 @@
         <v>0</v>
       </c>
       <c r="H476" t="n">
-        <v>51882.8</v>
+        <v>51472.79</v>
       </c>
       <c r="I476" t="n">
-        <v>52228.97</v>
+        <v>49865.13</v>
       </c>
       <c r="J476" t="n">
         <v>7</v>
@@ -19499,10 +19499,10 @@
         <v>0</v>
       </c>
       <c r="H477" t="n">
-        <v>56466.37</v>
+        <v>58812.39</v>
       </c>
       <c r="I477" t="n">
-        <v>56038.49</v>
+        <v>58603.42</v>
       </c>
       <c r="J477" t="n">
         <v>4</v>
@@ -19539,10 +19539,10 @@
         <v>0</v>
       </c>
       <c r="H478" t="n">
-        <v>50980.75</v>
+        <v>54979.87</v>
       </c>
       <c r="I478" t="n">
-        <v>51386.93</v>
+        <v>55119.31</v>
       </c>
       <c r="J478" t="n">
         <v>3</v>
@@ -19579,10 +19579,10 @@
         <v>0</v>
       </c>
       <c r="H479" t="n">
-        <v>92560.67999999999</v>
+        <v>80404.33</v>
       </c>
       <c r="I479" t="n">
-        <v>92277.97</v>
+        <v>79682.81</v>
       </c>
       <c r="J479" t="n">
         <v>15</v>
@@ -19619,10 +19619,10 @@
         <v>0</v>
       </c>
       <c r="H480" t="n">
-        <v>85315.95</v>
+        <v>76847.89999999999</v>
       </c>
       <c r="I480" t="n">
-        <v>85822.31</v>
+        <v>74812.72</v>
       </c>
       <c r="J480" t="n">
         <v>9</v>
@@ -19659,10 +19659,10 @@
         <v>0</v>
       </c>
       <c r="H481" t="n">
-        <v>81540.78999999999</v>
+        <v>78420.47</v>
       </c>
       <c r="I481" t="n">
-        <v>80503.55</v>
+        <v>77443.73</v>
       </c>
       <c r="J481" t="n">
         <v>6</v>
@@ -19699,10 +19699,10 @@
         <v>0</v>
       </c>
       <c r="H482" t="n">
-        <v>197794.74</v>
+        <v>235777.7</v>
       </c>
       <c r="I482" t="n">
-        <v>168141.03</v>
+        <v>199142.49</v>
       </c>
       <c r="J482" t="n">
         <v>23</v>
@@ -19739,10 +19739,10 @@
         <v>0</v>
       </c>
       <c r="H483" t="n">
-        <v>222048.56</v>
+        <v>213087.25</v>
       </c>
       <c r="I483" t="n">
-        <v>187798.27</v>
+        <v>179019.72</v>
       </c>
       <c r="J483" t="n">
         <v>14</v>
@@ -19779,10 +19779,10 @@
         <v>0</v>
       </c>
       <c r="H484" t="n">
-        <v>217335.24</v>
+        <v>218839.6</v>
       </c>
       <c r="I484" t="n">
-        <v>184704.31</v>
+        <v>185597.35</v>
       </c>
       <c r="J484" t="n">
         <v>9</v>
@@ -19819,10 +19819,10 @@
         <v>0</v>
       </c>
       <c r="H485" t="n">
-        <v>127764.89</v>
+        <v>90524.16</v>
       </c>
       <c r="I485" t="n">
-        <v>95414.3</v>
+        <v>90361.8</v>
       </c>
       <c r="J485" t="n">
         <v>11</v>
@@ -19859,10 +19859,10 @@
         <v>0</v>
       </c>
       <c r="H486" t="n">
-        <v>117978.03</v>
+        <v>98736.89</v>
       </c>
       <c r="I486" t="n">
-        <v>106986.97</v>
+        <v>99552.37</v>
       </c>
       <c r="J486" t="n">
         <v>6</v>
@@ -19899,10 +19899,10 @@
         <v>0</v>
       </c>
       <c r="H487" t="n">
-        <v>94799.55</v>
+        <v>113008.19</v>
       </c>
       <c r="I487" t="n">
-        <v>93163.03999999999</v>
+        <v>97881.57000000001</v>
       </c>
       <c r="J487" t="n">
         <v>4</v>
@@ -19936,13 +19936,13 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>280947.55</v>
+        <v>294252.16</v>
       </c>
       <c r="H488" t="n">
-        <v>89227.75999999999</v>
+        <v>77511.77</v>
       </c>
       <c r="I488" t="n">
-        <v>90332.77</v>
+        <v>76980.56</v>
       </c>
       <c r="J488" t="n">
         <v>20</v>
@@ -19976,13 +19976,13 @@
         </is>
       </c>
       <c r="G489" t="n">
-        <v>163685.1</v>
+        <v>183474.14</v>
       </c>
       <c r="H489" t="n">
-        <v>75997.36</v>
+        <v>68747.39</v>
       </c>
       <c r="I489" t="n">
-        <v>73884.48</v>
+        <v>68918.28999999999</v>
       </c>
       <c r="J489" t="n">
         <v>12</v>
@@ -20016,13 +20016,13 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>119841.59</v>
+        <v>122995.02</v>
       </c>
       <c r="H490" t="n">
-        <v>73979.66</v>
+        <v>67657.10000000001</v>
       </c>
       <c r="I490" t="n">
-        <v>74376.12</v>
+        <v>68464.39</v>
       </c>
       <c r="J490" t="n">
         <v>8</v>
@@ -20059,10 +20059,10 @@
         <v>0</v>
       </c>
       <c r="H491" t="n">
-        <v>54578.74</v>
+        <v>52150.48</v>
       </c>
       <c r="I491" t="n">
-        <v>54253.12</v>
+        <v>51914.94</v>
       </c>
       <c r="J491" t="n">
         <v>7</v>
@@ -20099,10 +20099,10 @@
         <v>0</v>
       </c>
       <c r="H492" t="n">
-        <v>53889.88</v>
+        <v>50022.82</v>
       </c>
       <c r="I492" t="n">
-        <v>54198.33</v>
+        <v>50209.51</v>
       </c>
       <c r="J492" t="n">
         <v>4</v>
@@ -20139,10 +20139,10 @@
         <v>0</v>
       </c>
       <c r="H493" t="n">
-        <v>50363.81</v>
+        <v>58631.28</v>
       </c>
       <c r="I493" t="n">
-        <v>50770.67</v>
+        <v>59093.37</v>
       </c>
       <c r="J493" t="n">
         <v>3</v>
@@ -20179,10 +20179,10 @@
         <v>0</v>
       </c>
       <c r="H494" t="n">
-        <v>81665.36</v>
+        <v>85973.27</v>
       </c>
       <c r="I494" t="n">
-        <v>84881.55</v>
+        <v>85501.75999999999</v>
       </c>
       <c r="J494" t="n">
         <v>15</v>
@@ -20219,10 +20219,10 @@
         <v>0</v>
       </c>
       <c r="H495" t="n">
-        <v>90193.25</v>
+        <v>82094.86</v>
       </c>
       <c r="I495" t="n">
-        <v>90586.95</v>
+        <v>80726.03</v>
       </c>
       <c r="J495" t="n">
         <v>9</v>
@@ -20259,10 +20259,10 @@
         <v>0</v>
       </c>
       <c r="H496" t="n">
-        <v>70992.16</v>
+        <v>78277.53</v>
       </c>
       <c r="I496" t="n">
-        <v>70072.59</v>
+        <v>77094.46000000001</v>
       </c>
       <c r="J496" t="n">
         <v>6</v>
@@ -20299,10 +20299,10 @@
         <v>0</v>
       </c>
       <c r="H497" t="n">
-        <v>211254.39</v>
+        <v>253837.5</v>
       </c>
       <c r="I497" t="n">
-        <v>178276.67</v>
+        <v>213925.3</v>
       </c>
       <c r="J497" t="n">
         <v>23</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="H498" t="n">
-        <v>217116.04</v>
+        <v>218921</v>
       </c>
       <c r="I498" t="n">
-        <v>182381.88</v>
+        <v>185823.51</v>
       </c>
       <c r="J498" t="n">
         <v>14</v>
@@ -20379,10 +20379,10 @@
         <v>0</v>
       </c>
       <c r="H499" t="n">
-        <v>194189.81</v>
+        <v>209730</v>
       </c>
       <c r="I499" t="n">
-        <v>163887.63</v>
+        <v>177043.22</v>
       </c>
       <c r="J499" t="n">
         <v>9</v>
@@ -20419,10 +20419,10 @@
         <v>0</v>
       </c>
       <c r="H500" t="n">
-        <v>90167.53999999999</v>
+        <v>98224.57000000001</v>
       </c>
       <c r="I500" t="n">
-        <v>89295.07000000001</v>
+        <v>97361.06</v>
       </c>
       <c r="J500" t="n">
         <v>11</v>
@@ -20459,10 +20459,10 @@
         <v>0</v>
       </c>
       <c r="H501" t="n">
-        <v>115062.39</v>
+        <v>91680.39999999999</v>
       </c>
       <c r="I501" t="n">
-        <v>96555.7</v>
+        <v>89163.12</v>
       </c>
       <c r="J501" t="n">
         <v>6</v>
@@ -20499,10 +20499,10 @@
         <v>0</v>
       </c>
       <c r="H502" t="n">
-        <v>143605.71</v>
+        <v>98530.25999999999</v>
       </c>
       <c r="I502" t="n">
-        <v>104780.27</v>
+        <v>101165.29</v>
       </c>
       <c r="J502" t="n">
         <v>4</v>
@@ -20536,13 +20536,13 @@
         </is>
       </c>
       <c r="G503" t="n">
-        <v>428637.74</v>
+        <v>444372.42</v>
       </c>
       <c r="H503" t="n">
-        <v>85091.44</v>
+        <v>67887.31</v>
       </c>
       <c r="I503" t="n">
-        <v>83175.03</v>
+        <v>67718.60000000001</v>
       </c>
       <c r="J503" t="n">
         <v>20</v>
@@ -20576,13 +20576,13 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>278840.27</v>
+        <v>266605.12</v>
       </c>
       <c r="H504" t="n">
-        <v>76959</v>
+        <v>73317.57000000001</v>
       </c>
       <c r="I504" t="n">
-        <v>78588.11</v>
+        <v>72764.64</v>
       </c>
       <c r="J504" t="n">
         <v>12</v>
@@ -20616,13 +20616,13 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>170664.11</v>
+        <v>185193.96</v>
       </c>
       <c r="H505" t="n">
-        <v>73494.89999999999</v>
+        <v>70475.74000000001</v>
       </c>
       <c r="I505" t="n">
-        <v>73298.16</v>
+        <v>70281.88</v>
       </c>
       <c r="J505" t="n">
         <v>8</v>
@@ -20659,10 +20659,10 @@
         <v>0</v>
       </c>
       <c r="H506" t="n">
-        <v>55167.17</v>
+        <v>59358.99</v>
       </c>
       <c r="I506" t="n">
-        <v>55443.98</v>
+        <v>60390.43</v>
       </c>
       <c r="J506" t="n">
         <v>7</v>
@@ -20699,10 +20699,10 @@
         <v>0</v>
       </c>
       <c r="H507" t="n">
-        <v>56596.45</v>
+        <v>54341.56</v>
       </c>
       <c r="I507" t="n">
-        <v>56061.88</v>
+        <v>55253.53</v>
       </c>
       <c r="J507" t="n">
         <v>4</v>
@@ -20739,10 +20739,10 @@
         <v>0</v>
       </c>
       <c r="H508" t="n">
-        <v>54440.75</v>
+        <v>57035.43</v>
       </c>
       <c r="I508" t="n">
-        <v>54467.18</v>
+        <v>56653.07</v>
       </c>
       <c r="J508" t="n">
         <v>3</v>
@@ -20779,10 +20779,10 @@
         <v>0</v>
       </c>
       <c r="H509" t="n">
-        <v>93876.64</v>
+        <v>92575.03</v>
       </c>
       <c r="I509" t="n">
-        <v>92842.48</v>
+        <v>90202.25999999999</v>
       </c>
       <c r="J509" t="n">
         <v>15</v>
@@ -20819,10 +20819,10 @@
         <v>0</v>
       </c>
       <c r="H510" t="n">
-        <v>84051.03</v>
+        <v>93776.98</v>
       </c>
       <c r="I510" t="n">
-        <v>85530.96000000001</v>
+        <v>94218.03999999999</v>
       </c>
       <c r="J510" t="n">
         <v>9</v>
@@ -20859,10 +20859,10 @@
         <v>0</v>
       </c>
       <c r="H511" t="n">
-        <v>85348.58</v>
+        <v>84782.14999999999</v>
       </c>
       <c r="I511" t="n">
-        <v>83119.03999999999</v>
+        <v>83954.24000000001</v>
       </c>
       <c r="J511" t="n">
         <v>6</v>
@@ -20899,10 +20899,10 @@
         <v>0</v>
       </c>
       <c r="H512" t="n">
-        <v>222396.68</v>
+        <v>210731.6</v>
       </c>
       <c r="I512" t="n">
-        <v>188141.83</v>
+        <v>177910.9</v>
       </c>
       <c r="J512" t="n">
         <v>23</v>
@@ -20939,10 +20939,10 @@
         <v>0</v>
       </c>
       <c r="H513" t="n">
-        <v>195519.96</v>
+        <v>199617.74</v>
       </c>
       <c r="I513" t="n">
-        <v>164797.6</v>
+        <v>169271.63</v>
       </c>
       <c r="J513" t="n">
         <v>14</v>
@@ -20979,10 +20979,10 @@
         <v>0</v>
       </c>
       <c r="H514" t="n">
-        <v>210398.83</v>
+        <v>240309.14</v>
       </c>
       <c r="I514" t="n">
-        <v>176964.47</v>
+        <v>201816.26</v>
       </c>
       <c r="J514" t="n">
         <v>9</v>
@@ -21019,10 +21019,10 @@
         <v>0</v>
       </c>
       <c r="H515" t="n">
-        <v>95702.55</v>
+        <v>94617.67</v>
       </c>
       <c r="I515" t="n">
-        <v>96613.78</v>
+        <v>92604.3</v>
       </c>
       <c r="J515" t="n">
         <v>11</v>
@@ -21059,10 +21059,10 @@
         <v>0</v>
       </c>
       <c r="H516" t="n">
-        <v>82255.83</v>
+        <v>92040.28999999999</v>
       </c>
       <c r="I516" t="n">
-        <v>82751.49000000001</v>
+        <v>93222.59</v>
       </c>
       <c r="J516" t="n">
         <v>6</v>
@@ -21099,10 +21099,10 @@
         <v>0</v>
       </c>
       <c r="H517" t="n">
-        <v>102673.95</v>
+        <v>128996.89</v>
       </c>
       <c r="I517" t="n">
-        <v>102921.45</v>
+        <v>105645.95</v>
       </c>
       <c r="J517" t="n">
         <v>4</v>
@@ -21136,13 +21136,13 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>422501.5</v>
+        <v>428919.85</v>
       </c>
       <c r="H518" t="n">
-        <v>81238.61</v>
+        <v>80468.98</v>
       </c>
       <c r="I518" t="n">
-        <v>81499.88</v>
+        <v>78111.47</v>
       </c>
       <c r="J518" t="n">
         <v>20</v>
@@ -21176,13 +21176,13 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>269196.49</v>
+        <v>274759.05</v>
       </c>
       <c r="H519" t="n">
-        <v>80792.32000000001</v>
+        <v>73995.06</v>
       </c>
       <c r="I519" t="n">
-        <v>81685.19</v>
+        <v>73201.74000000001</v>
       </c>
       <c r="J519" t="n">
         <v>12</v>
@@ -21216,13 +21216,13 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>173471.46</v>
+        <v>194087.94</v>
       </c>
       <c r="H520" t="n">
-        <v>78982.09</v>
+        <v>84687.98</v>
       </c>
       <c r="I520" t="n">
-        <v>79802.06</v>
+        <v>84192.03999999999</v>
       </c>
       <c r="J520" t="n">
         <v>8</v>
@@ -21259,10 +21259,10 @@
         <v>0</v>
       </c>
       <c r="H521" t="n">
-        <v>50996.96</v>
+        <v>48484.53</v>
       </c>
       <c r="I521" t="n">
-        <v>50735.42</v>
+        <v>49366.74</v>
       </c>
       <c r="J521" t="n">
         <v>7</v>
@@ -21299,10 +21299,10 @@
         <v>0</v>
       </c>
       <c r="H522" t="n">
-        <v>59445.76</v>
+        <v>52037.38</v>
       </c>
       <c r="I522" t="n">
-        <v>58800.6</v>
+        <v>51599.07</v>
       </c>
       <c r="J522" t="n">
         <v>4</v>
@@ -21339,10 +21339,10 @@
         <v>0</v>
       </c>
       <c r="H523" t="n">
-        <v>60879.88</v>
+        <v>56258.47</v>
       </c>
       <c r="I523" t="n">
-        <v>59465.58</v>
+        <v>55956.93</v>
       </c>
       <c r="J523" t="n">
         <v>3</v>
@@ -21379,10 +21379,10 @@
         <v>0</v>
       </c>
       <c r="H524" t="n">
-        <v>83288.12</v>
+        <v>79535.95</v>
       </c>
       <c r="I524" t="n">
-        <v>83766.64999999999</v>
+        <v>81043.2</v>
       </c>
       <c r="J524" t="n">
         <v>15</v>
@@ -21419,10 +21419,10 @@
         <v>0</v>
       </c>
       <c r="H525" t="n">
-        <v>91197.12</v>
+        <v>81079.62</v>
       </c>
       <c r="I525" t="n">
-        <v>88565.2</v>
+        <v>81390.74000000001</v>
       </c>
       <c r="J525" t="n">
         <v>9</v>
@@ -21459,10 +21459,10 @@
         <v>0</v>
       </c>
       <c r="H526" t="n">
-        <v>86949.39</v>
+        <v>78816.77</v>
       </c>
       <c r="I526" t="n">
-        <v>87785.77</v>
+        <v>80253.74000000001</v>
       </c>
       <c r="J526" t="n">
         <v>6</v>
@@ -21499,10 +21499,10 @@
         <v>0</v>
       </c>
       <c r="H527" t="n">
-        <v>227297.5</v>
+        <v>182626.84</v>
       </c>
       <c r="I527" t="n">
-        <v>192192.27</v>
+        <v>153108.51</v>
       </c>
       <c r="J527" t="n">
         <v>23</v>
@@ -21539,10 +21539,10 @@
         <v>0</v>
       </c>
       <c r="H528" t="n">
-        <v>208876.74</v>
+        <v>189812.69</v>
       </c>
       <c r="I528" t="n">
-        <v>175798.56</v>
+        <v>161219.99</v>
       </c>
       <c r="J528" t="n">
         <v>14</v>
@@ -21579,10 +21579,10 @@
         <v>0</v>
       </c>
       <c r="H529" t="n">
-        <v>198985.37</v>
+        <v>222278.87</v>
       </c>
       <c r="I529" t="n">
-        <v>167928.74</v>
+        <v>188025.86</v>
       </c>
       <c r="J529" t="n">
         <v>9</v>
@@ -21619,10 +21619,10 @@
         <v>0</v>
       </c>
       <c r="H530" t="n">
-        <v>102319.2</v>
+        <v>108203.33</v>
       </c>
       <c r="I530" t="n">
-        <v>102731.38</v>
+        <v>91016.02</v>
       </c>
       <c r="J530" t="n">
         <v>11</v>
@@ -21659,10 +21659,10 @@
         <v>0</v>
       </c>
       <c r="H531" t="n">
-        <v>88011.71000000001</v>
+        <v>100574.93</v>
       </c>
       <c r="I531" t="n">
-        <v>88798.41</v>
+        <v>100455.9</v>
       </c>
       <c r="J531" t="n">
         <v>6</v>
@@ -21699,10 +21699,10 @@
         <v>0</v>
       </c>
       <c r="H532" t="n">
-        <v>108029.24</v>
+        <v>95051.77</v>
       </c>
       <c r="I532" t="n">
-        <v>89700.39999999999</v>
+        <v>89876.58</v>
       </c>
       <c r="J532" t="n">
         <v>4</v>
@@ -21736,13 +21736,13 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>445952.46</v>
+        <v>423953.84</v>
       </c>
       <c r="H533" t="n">
-        <v>75578.49000000001</v>
+        <v>90221.91</v>
       </c>
       <c r="I533" t="n">
-        <v>76812.64999999999</v>
+        <v>92121.17999999999</v>
       </c>
       <c r="J533" t="n">
         <v>20</v>
@@ -21776,13 +21776,13 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>256610.69</v>
+        <v>273451.62</v>
       </c>
       <c r="H534" t="n">
-        <v>73718.39999999999</v>
+        <v>74609.5</v>
       </c>
       <c r="I534" t="n">
-        <v>73111.11</v>
+        <v>73965.52</v>
       </c>
       <c r="J534" t="n">
         <v>12</v>
@@ -21816,13 +21816,13 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>169481.17</v>
+        <v>178268.4</v>
       </c>
       <c r="H535" t="n">
-        <v>74212.24000000001</v>
+        <v>75636.34</v>
       </c>
       <c r="I535" t="n">
-        <v>75472.72</v>
+        <v>76518.11</v>
       </c>
       <c r="J535" t="n">
         <v>8</v>
@@ -21859,10 +21859,10 @@
         <v>0</v>
       </c>
       <c r="H536" t="n">
-        <v>53642.17</v>
+        <v>55718.72</v>
       </c>
       <c r="I536" t="n">
-        <v>53825.94</v>
+        <v>54358.91</v>
       </c>
       <c r="J536" t="n">
         <v>7</v>
@@ -21899,10 +21899,10 @@
         <v>0</v>
       </c>
       <c r="H537" t="n">
-        <v>57200.14</v>
+        <v>56004.79</v>
       </c>
       <c r="I537" t="n">
-        <v>57711.74</v>
+        <v>56386.79</v>
       </c>
       <c r="J537" t="n">
         <v>4</v>
@@ -21939,10 +21939,10 @@
         <v>0</v>
       </c>
       <c r="H538" t="n">
-        <v>52364.23</v>
+        <v>55407.46</v>
       </c>
       <c r="I538" t="n">
-        <v>52037.91</v>
+        <v>53885.78</v>
       </c>
       <c r="J538" t="n">
         <v>3</v>
@@ -21979,10 +21979,10 @@
         <v>0</v>
       </c>
       <c r="H539" t="n">
-        <v>90121.59</v>
+        <v>89299.84</v>
       </c>
       <c r="I539" t="n">
-        <v>91909.09</v>
+        <v>89828.24000000001</v>
       </c>
       <c r="J539" t="n">
         <v>15</v>
@@ -22019,10 +22019,10 @@
         <v>0</v>
       </c>
       <c r="H540" t="n">
-        <v>78893.69</v>
+        <v>86850.97</v>
       </c>
       <c r="I540" t="n">
-        <v>77556.03</v>
+        <v>84144.82000000001</v>
       </c>
       <c r="J540" t="n">
         <v>9</v>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="H541" t="n">
-        <v>80216.55</v>
+        <v>78265.89</v>
       </c>
       <c r="I541" t="n">
-        <v>79848.83</v>
+        <v>78533.89</v>
       </c>
       <c r="J541" t="n">
         <v>6</v>
